--- a/src/datos/SuitePruebas.xlsx
+++ b/src/datos/SuitePruebas.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\AutomatizacionAF\src\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6EB752-E01D-41A4-9464-A7BB942EA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A155A4FD-CB18-4AB7-A46C-1480329278F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-156" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CotizadorAF" sheetId="1" r:id="rId1"/>
     <sheet name="EmisionAF" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="121">
   <si>
     <t>EscenarioPrueba</t>
   </si>
@@ -114,18 +115,9 @@
     <t>`</t>
   </si>
   <si>
-    <t>Cotizacion Uno</t>
-  </si>
-  <si>
     <t>Url</t>
   </si>
   <si>
-    <t>Cotizacion Dos</t>
-  </si>
-  <si>
-    <t>Cotizacion Tres</t>
-  </si>
-  <si>
     <t>https://weeqp.azurewebsites.net/AF/Broker/Login/Auth</t>
   </si>
   <si>
@@ -159,166 +151,256 @@
     <t>CotizarPlan</t>
   </si>
   <si>
+    <t>FrecuenciaPago</t>
+  </si>
+  <si>
+    <t>RedProveedores</t>
+  </si>
+  <si>
+    <t>Deducible</t>
+  </si>
+  <si>
+    <t>$1,000.00 / $3,000.00 USD</t>
+  </si>
+  <si>
+    <t>Ultra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Masculino</t>
+  </si>
+  <si>
+    <t>Femenino</t>
+  </si>
+  <si>
+    <t>Soltero(a)</t>
+  </si>
+  <si>
+    <t>Arte/Entretenimiento/Medios</t>
+  </si>
+  <si>
+    <t>Hijo1</t>
+  </si>
+  <si>
+    <t>Hijo2</t>
+  </si>
+  <si>
+    <t>Hijo3</t>
+  </si>
+  <si>
+    <t>Hijo4</t>
+  </si>
+  <si>
+    <t>Hijo5</t>
+  </si>
+  <si>
+    <t>Hijo Biológico</t>
+  </si>
+  <si>
+    <t>Hijastro</t>
+  </si>
+  <si>
+    <t>Hijo Adoptado Legalmente</t>
+  </si>
+  <si>
+    <t>Menor Bajo Custodia Legal</t>
+  </si>
+  <si>
+    <t>Cónyuge/Pareja Doméstica</t>
+  </si>
+  <si>
+    <t>SexoAlNacer</t>
+  </si>
+  <si>
+    <t>TelefonoSecundario</t>
+  </si>
+  <si>
+    <t>EliminarTelSec</t>
+  </si>
+  <si>
+    <t>OcupacionTitular</t>
+  </si>
+  <si>
+    <t>TipoIdentificacionTitular</t>
+  </si>
+  <si>
+    <t>ID del país</t>
+  </si>
+  <si>
+    <t>DireccionCorrespondencia</t>
+  </si>
+  <si>
+    <t>EliminarDirCorr</t>
+  </si>
+  <si>
+    <t>SexoDependiente1</t>
+  </si>
+  <si>
+    <t>SexoDependiente2</t>
+  </si>
+  <si>
+    <t>SexoDependiente3</t>
+  </si>
+  <si>
+    <t>SexoDependiente4</t>
+  </si>
+  <si>
+    <t>SexoDependiente5</t>
+  </si>
+  <si>
+    <t>RelacionSolicitantePrimario</t>
+  </si>
+  <si>
+    <t>P5Sustancia</t>
+  </si>
+  <si>
+    <t>Productos de Nicotina</t>
+  </si>
+  <si>
+    <t>SigueIngiriendo</t>
+  </si>
+  <si>
+    <t>CuestionarioMedicoCaptura</t>
+  </si>
+  <si>
+    <t>https://weeqp.azurewebsites.net/QP/WeeClaims/#/Emision</t>
+  </si>
+  <si>
+    <t>pruebasxj@yopmail.com</t>
+  </si>
+  <si>
+    <t>Emision 1</t>
+  </si>
+  <si>
+    <t>UrlClaims</t>
+  </si>
+  <si>
+    <t>CorreoClaims</t>
+  </si>
+  <si>
+    <t>ContrasenaClaims</t>
+  </si>
+  <si>
+    <t>FolioSolicitante</t>
+  </si>
+  <si>
+    <t>923000003343</t>
+  </si>
+  <si>
+    <t>qahomxj1broker@yopmail.com</t>
+  </si>
+  <si>
+    <t>CapturaPreguntasPt2</t>
+  </si>
+  <si>
+    <t>Superior</t>
+  </si>
+  <si>
+    <t>Trimestral</t>
+  </si>
+  <si>
+    <t>Mensual</t>
+  </si>
+  <si>
+    <t>$2,000.00 / $4,000.00 US</t>
+  </si>
+  <si>
+    <t>$5,000.00 / $5,000.00 USD</t>
+  </si>
+  <si>
+    <t>$5,000.00 / $7,500.00 USD</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Cotizacion Superior Ultra Trimestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Superior Ultra Mensual</t>
+  </si>
+  <si>
+    <t>Cotizacion Superior Open Anual</t>
+  </si>
+  <si>
+    <t>Cotizacion Superior Open Semestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Superior Open Trimestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Optima Ultra Anual</t>
+  </si>
+  <si>
+    <t>Cotizacion Optima Ultra Semestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Optima Ultra Trimestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Optima Ultra Mensual</t>
+  </si>
+  <si>
     <t>Optima</t>
   </si>
   <si>
-    <t>FrecuenciaPago</t>
-  </si>
-  <si>
-    <t>RedProveedores</t>
-  </si>
-  <si>
-    <t>Deducible</t>
-  </si>
-  <si>
-    <t>$1,000.00 / $3,000.00 USD</t>
+    <t>Plus</t>
+  </si>
+  <si>
+    <t>Cotizacion Vital Plus Anual</t>
+  </si>
+  <si>
+    <t>Cotizacion  Vital Plus Semestral</t>
+  </si>
+  <si>
+    <t>Cotizacion  Vital Plus Trimestral</t>
+  </si>
+  <si>
+    <t>Cotizacion  Vital Plus Mensual</t>
+  </si>
+  <si>
+    <t>Cotizacion Vital Core Anual</t>
+  </si>
+  <si>
+    <t>Cotizacion Vital Core Semestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Vital Core Trimestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Vital Core Mensual</t>
+  </si>
+  <si>
+    <t>Core</t>
+  </si>
+  <si>
+    <t>Vital</t>
+  </si>
+  <si>
+    <t>Cotizacion Superior Ultra Semestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Superior Ultra Anual</t>
+  </si>
+  <si>
+    <t>Cotizacion Superior Open Mensual</t>
   </si>
   <si>
     <t>Eng</t>
   </si>
   <si>
-    <t>Port</t>
-  </si>
-  <si>
-    <t>Ultra</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Masculino</t>
-  </si>
-  <si>
-    <t>Femenino</t>
-  </si>
-  <si>
-    <t>Soltero(a)</t>
-  </si>
-  <si>
-    <t>Arte/Entretenimiento/Medios</t>
-  </si>
-  <si>
-    <t>Hijo1</t>
-  </si>
-  <si>
-    <t>Hijo2</t>
-  </si>
-  <si>
-    <t>Hijo3</t>
-  </si>
-  <si>
-    <t>Hijo4</t>
-  </si>
-  <si>
-    <t>Hijo5</t>
-  </si>
-  <si>
-    <t>Hijo Biológico</t>
-  </si>
-  <si>
-    <t>Hijastro</t>
-  </si>
-  <si>
-    <t>Hijo Adoptado Legalmente</t>
-  </si>
-  <si>
-    <t>Menor Bajo Custodia Legal</t>
-  </si>
-  <si>
-    <t>Cónyuge/Pareja Doméstica</t>
-  </si>
-  <si>
-    <t>SexoAlNacer</t>
-  </si>
-  <si>
-    <t>TelefonoSecundario</t>
-  </si>
-  <si>
-    <t>EliminarTelSec</t>
-  </si>
-  <si>
-    <t>OcupacionTitular</t>
-  </si>
-  <si>
-    <t>TipoIdentificacionTitular</t>
-  </si>
-  <si>
-    <t>ID del país</t>
-  </si>
-  <si>
-    <t>DireccionCorrespondencia</t>
-  </si>
-  <si>
-    <t>EliminarDirCorr</t>
-  </si>
-  <si>
-    <t>SexoDependiente1</t>
-  </si>
-  <si>
-    <t>SexoDependiente2</t>
-  </si>
-  <si>
-    <t>SexoDependiente3</t>
-  </si>
-  <si>
-    <t>SexoDependiente4</t>
-  </si>
-  <si>
-    <t>SexoDependiente5</t>
-  </si>
-  <si>
-    <t>RelacionSolicitantePrimario</t>
-  </si>
-  <si>
-    <t>P5Sustancia</t>
-  </si>
-  <si>
-    <t>Productos de Nicotina</t>
-  </si>
-  <si>
-    <t>SigueIngiriendo</t>
-  </si>
-  <si>
-    <t>CuestionarioMedicoCaptura</t>
-  </si>
-  <si>
-    <t>https://weeqp.azurewebsites.net/QP/WeeClaims/#/Emision</t>
-  </si>
-  <si>
-    <t>pruebasxj@yopmail.com</t>
-  </si>
-  <si>
-    <t>Emision 1</t>
-  </si>
-  <si>
-    <t>UrlClaims</t>
-  </si>
-  <si>
-    <t>CorreoClaims</t>
-  </si>
-  <si>
-    <t>ContrasenaClaims</t>
-  </si>
-  <si>
-    <t>FolioSolicitante</t>
-  </si>
-  <si>
-    <t>923000003343</t>
-  </si>
-  <si>
-    <t>qahomxj1broker@yopmail.com</t>
-  </si>
-  <si>
-    <t>Cotizacion Cuatro</t>
-  </si>
-  <si>
-    <t>Cotizacion Cinco</t>
-  </si>
-  <si>
-    <t>Cotizacion Seis</t>
-  </si>
-  <si>
-    <t>CapturaPreguntasPt2</t>
+    <t>Cotizacion Optima Plus Anual</t>
+  </si>
+  <si>
+    <t>Cotizacion Optima Plus Semestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Optima Plus Trimestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Optima Plus Mensual</t>
   </si>
 </sst>
 </file>
@@ -360,12 +442,18 @@
       <name val="Poppins"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -382,7 +470,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -391,6 +479,8 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -730,7 +820,7 @@
   <dimension ref="A1:DM13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
@@ -846,106 +936,106 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" t="s">
-        <v>35</v>
-      </c>
       <c r="G1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L1" t="s">
-        <v>41</v>
-      </c>
       <c r="M1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N1" t="s">
         <v>1</v>
       </c>
       <c r="O1" t="s">
+        <v>58</v>
+      </c>
+      <c r="P1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>60</v>
+      </c>
+      <c r="R1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S1" t="s">
+        <v>63</v>
+      </c>
+      <c r="T1" t="s">
         <v>64</v>
       </c>
-      <c r="P1" t="s">
+      <c r="U1" t="s">
+        <v>47</v>
+      </c>
+      <c r="V1" t="s">
         <v>65</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="W1" t="s">
+        <v>48</v>
+      </c>
+      <c r="X1" t="s">
         <v>66</v>
       </c>
-      <c r="R1" t="s">
+      <c r="Y1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z1" t="s">
         <v>67</v>
       </c>
-      <c r="S1" t="s">
+      <c r="AA1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD1" t="s">
         <v>69</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AE1" t="s">
         <v>70</v>
       </c>
-      <c r="U1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="AF1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG1" t="s">
         <v>71</v>
       </c>
-      <c r="W1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z1" t="s">
+      <c r="AH1" t="s">
         <v>73</v>
       </c>
-      <c r="AA1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>79</v>
-      </c>
       <c r="AI1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="AR1" t="s">
         <v>13</v>
@@ -994,20 +1084,20 @@
       </c>
     </row>
     <row r="2" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>25</v>
+      <c r="A2" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -1016,25 +1106,25 @@
         <v>5</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K2" t="s">
         <v>40</v>
       </c>
-      <c r="J2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2" t="s">
-        <v>44</v>
-      </c>
       <c r="L2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="O2" t="s">
         <v>6</v>
@@ -1043,10 +1133,10 @@
         <v>5</v>
       </c>
       <c r="Q2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="R2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="S2" t="s">
         <v>6</v>
@@ -1055,43 +1145,43 @@
         <v>5</v>
       </c>
       <c r="U2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="V2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="X2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="Z2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="AA2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AC2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AD2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AE2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AF2" t="s">
         <v>6</v>
       </c>
       <c r="AG2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH2" t="s">
         <v>6</v>
@@ -1150,20 +1240,20 @@
       </c>
     </row>
     <row r="3" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>27</v>
+      <c r="A3" s="9" t="s">
+        <v>104</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1172,25 +1262,25 @@
         <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="K3" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s">
         <v>4</v>
       </c>
       <c r="M3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="O3" t="s">
         <v>6</v>
@@ -1199,10 +1289,10 @@
         <v>5</v>
       </c>
       <c r="Q3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="R3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="S3" t="s">
         <v>6</v>
@@ -1211,46 +1301,49 @@
         <v>5</v>
       </c>
       <c r="U3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="V3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="X3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="Z3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="AA3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AB3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AC3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AD3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AE3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AF3" t="s">
         <v>6</v>
       </c>
       <c r="AG3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH3" t="s">
         <v>6</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>5</v>
       </c>
       <c r="AK3" s="4"/>
       <c r="AM3" s="3"/>
@@ -1303,20 +1396,20 @@
       </c>
     </row>
     <row r="4" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>28</v>
+      <c r="A4" s="9" t="s">
+        <v>105</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -1325,25 +1418,25 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I4" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="J4" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="K4" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="L4" t="s">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="M4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="O4" t="s">
         <v>6</v>
@@ -1352,10 +1445,10 @@
         <v>5</v>
       </c>
       <c r="Q4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="R4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="S4" t="s">
         <v>6</v>
@@ -1364,46 +1457,49 @@
         <v>5</v>
       </c>
       <c r="U4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="V4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="X4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="Z4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="AA4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AC4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AD4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AE4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AF4" t="s">
         <v>6</v>
       </c>
       <c r="AG4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH4" t="s">
         <v>6</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>5</v>
       </c>
       <c r="AK4" s="4"/>
       <c r="AM4" s="3"/>
@@ -1456,20 +1552,20 @@
       </c>
     </row>
     <row r="5" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>90</v>
+      <c r="A5" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -1478,25 +1574,25 @@
         <v>5</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="J5" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="K5" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="L5" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="M5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="O5" t="s">
         <v>6</v>
@@ -1505,10 +1601,10 @@
         <v>5</v>
       </c>
       <c r="Q5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="R5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="S5" t="s">
         <v>6</v>
@@ -1517,63 +1613,66 @@
         <v>5</v>
       </c>
       <c r="U5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="V5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="X5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="Z5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="AA5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AB5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AC5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AD5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AE5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AF5" t="s">
         <v>6</v>
       </c>
       <c r="AG5" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH5" t="s">
         <v>6</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>91</v>
+      <c r="A6" s="9" t="s">
+        <v>107</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -1582,25 +1681,25 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" t="s">
+        <v>111</v>
+      </c>
+      <c r="K6" t="s">
         <v>40</v>
       </c>
-      <c r="J6" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" t="s">
-        <v>44</v>
-      </c>
       <c r="L6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="O6" t="s">
         <v>6</v>
@@ -1609,10 +1708,10 @@
         <v>5</v>
       </c>
       <c r="Q6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="R6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="S6" t="s">
         <v>6</v>
@@ -1621,64 +1720,115 @@
         <v>5</v>
       </c>
       <c r="U6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="V6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="W6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="X6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="Z6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="AA6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AB6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AC6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AD6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AE6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AF6" t="s">
         <v>6</v>
       </c>
       <c r="AG6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH6" t="s">
         <v>6</v>
       </c>
-      <c r="DM6" s="2"/>
+      <c r="AI6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK6" s="4"/>
+      <c r="AM6" s="3"/>
+      <c r="AO6" s="3"/>
+      <c r="AP6" s="3"/>
+      <c r="AR6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX6">
+        <v>100</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ6">
+        <v>25</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB6">
+        <v>20</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD6">
+        <v>20</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF6">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>92</v>
+      <c r="A7" s="9" t="s">
+        <v>108</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -1687,25 +1837,25 @@
         <v>5</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="K7" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="L7" t="s">
         <v>4</v>
       </c>
       <c r="M7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="O7" t="s">
         <v>6</v>
@@ -1714,10 +1864,10 @@
         <v>5</v>
       </c>
       <c r="Q7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="R7" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="S7" t="s">
         <v>6</v>
@@ -1726,52 +1876,362 @@
         <v>5</v>
       </c>
       <c r="U7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="V7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="W7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="X7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="Z7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="AA7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AC7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AD7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AE7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK7" s="4"/>
+      <c r="AM7" s="3"/>
+      <c r="AO7" s="3"/>
+      <c r="AP7" s="3"/>
+      <c r="AR7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX7">
+        <v>100</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ7">
+        <v>25</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB7">
+        <v>20</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD7">
+        <v>20</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L8" t="s">
+        <v>86</v>
+      </c>
+      <c r="M8" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P8" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>46</v>
+      </c>
+      <c r="R8" t="s">
         <v>62</v>
       </c>
-      <c r="AF7" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>6</v>
-      </c>
-      <c r="DM7" s="2"/>
+      <c r="S8" t="s">
+        <v>6</v>
+      </c>
+      <c r="T8" t="s">
+        <v>5</v>
+      </c>
+      <c r="U8" t="s">
+        <v>52</v>
+      </c>
+      <c r="V8" t="s">
+        <v>43</v>
+      </c>
+      <c r="W8" t="s">
+        <v>53</v>
+      </c>
+      <c r="X8" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK8" s="4"/>
+      <c r="AM8" s="3"/>
+      <c r="AO8" s="3"/>
+      <c r="AP8" s="3"/>
+      <c r="AR8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX8">
+        <v>100</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ8">
+        <v>25</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB8">
+        <v>20</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD8">
+        <v>20</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF8">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="AU9" s="2"/>
-      <c r="DM9" s="2"/>
+      <c r="A9" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" t="s">
+        <v>111</v>
+      </c>
+      <c r="K9" t="s">
+        <v>90</v>
+      </c>
+      <c r="L9" t="s">
+        <v>87</v>
+      </c>
+      <c r="M9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" t="s">
+        <v>6</v>
+      </c>
+      <c r="P9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>46</v>
+      </c>
+      <c r="R9" t="s">
+        <v>62</v>
+      </c>
+      <c r="S9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" t="s">
+        <v>52</v>
+      </c>
+      <c r="V9" t="s">
+        <v>43</v>
+      </c>
+      <c r="W9" t="s">
+        <v>53</v>
+      </c>
+      <c r="X9" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:117" x14ac:dyDescent="0.25">
       <c r="AU10" s="2"/>
@@ -1779,7 +2239,7 @@
     </row>
     <row r="11" spans="1:117" x14ac:dyDescent="0.25">
       <c r="G11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AU11" s="2"/>
     </row>
@@ -1799,18 +2259,21 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{0C92C0F9-A7AE-4D03-89F5-B286F2CC67BE}"/>
-    <hyperlink ref="D2" r:id="rId2" xr:uid="{C086842D-1602-4388-B16E-8B35D98150B3}"/>
-    <hyperlink ref="B3:B6" r:id="rId3" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{45957601-23AD-4501-AF0F-DD07D06BBC14}"/>
-    <hyperlink ref="B7" r:id="rId4" xr:uid="{1C5F4854-8468-4956-AB85-8C23F53DC53A}"/>
-    <hyperlink ref="D3" r:id="rId5" xr:uid="{F6FA0EE4-4810-4469-AA62-8248A52A0517}"/>
-    <hyperlink ref="D4" r:id="rId6" xr:uid="{1480D6B5-121E-46AB-98A2-9195F59438CE}"/>
-    <hyperlink ref="D5" r:id="rId7" xr:uid="{5A24B62D-E43E-4FE0-8B18-0A7DE3231746}"/>
-    <hyperlink ref="D6" r:id="rId8" xr:uid="{9BAE2AD1-3FEC-4A40-8BE1-EA2CA7BF14F9}"/>
-    <hyperlink ref="D7" r:id="rId9" xr:uid="{A85CD6C5-83F9-42E3-A66D-CC9DEA252AB0}"/>
+    <hyperlink ref="B6:B9" r:id="rId1" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{45957601-23AD-4501-AF0F-DD07D06BBC14}"/>
+    <hyperlink ref="B6" r:id="rId2" xr:uid="{46F897B8-AEA5-46E4-9E00-38627D387AAE}"/>
+    <hyperlink ref="D6" r:id="rId3" xr:uid="{06A466C3-D169-424D-8ED2-BB4617F2FFC9}"/>
+    <hyperlink ref="B7:B9" r:id="rId4" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{88DDC58F-C538-415D-B24B-CDFEA094129F}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{68764909-E72A-4A4D-86DF-5924CA779A40}"/>
+    <hyperlink ref="D8" r:id="rId6" xr:uid="{E0FE90CB-C96E-4567-8471-28ACB3673D10}"/>
+    <hyperlink ref="D9" r:id="rId7" xr:uid="{7487188D-D7A9-4D3A-8893-B8B69F54129E}"/>
+    <hyperlink ref="B2" r:id="rId8" xr:uid="{0C92C0F9-A7AE-4D03-89F5-B286F2CC67BE}"/>
+    <hyperlink ref="D2" r:id="rId9" xr:uid="{C086842D-1602-4388-B16E-8B35D98150B3}"/>
+    <hyperlink ref="D3" r:id="rId10" xr:uid="{F6FA0EE4-4810-4469-AA62-8248A52A0517}"/>
+    <hyperlink ref="D4" r:id="rId11" xr:uid="{1480D6B5-121E-46AB-98A2-9195F59438CE}"/>
+    <hyperlink ref="D5" r:id="rId12" xr:uid="{5A24B62D-E43E-4FE0-8B18-0A7DE3231746}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
 
@@ -1831,34 +2294,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AE1" s="5"/>
     </row>
     <row r="2" spans="1:31" ht="21.75" x14ac:dyDescent="0.6">
       <c r="A2" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>88</v>
       </c>
       <c r="AE2" s="5"/>
     </row>
@@ -1875,4 +2338,3510 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89217B83-F5AC-41B7-85ED-07DFA2DFDFF5}">
+  <dimension ref="A1:BF24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R1" t="s">
+        <v>62</v>
+      </c>
+      <c r="S1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V1" t="s">
+        <v>43</v>
+      </c>
+      <c r="W1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK1" s="4"/>
+      <c r="AM1" s="3"/>
+      <c r="AO1" s="3"/>
+      <c r="AP1" s="3"/>
+      <c r="AR1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX1">
+        <v>100</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ1">
+        <v>25</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB1">
+        <v>20</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD1">
+        <v>20</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R2" t="s">
+        <v>62</v>
+      </c>
+      <c r="S2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T2" t="s">
+        <v>5</v>
+      </c>
+      <c r="U2" t="s">
+        <v>52</v>
+      </c>
+      <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK2" s="4"/>
+      <c r="AM2" s="3"/>
+      <c r="AO2" s="3"/>
+      <c r="AP2" s="3"/>
+      <c r="AR2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX2">
+        <v>100</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ2">
+        <v>25</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB2">
+        <v>20</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD2">
+        <v>20</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" t="s">
+        <v>62</v>
+      </c>
+      <c r="S3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U3" t="s">
+        <v>52</v>
+      </c>
+      <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK3" s="4"/>
+      <c r="AM3" s="3"/>
+      <c r="AO3" s="3"/>
+      <c r="AP3" s="3"/>
+      <c r="AR3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX3">
+        <v>100</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ3">
+        <v>25</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB3">
+        <v>20</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD3">
+        <v>20</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" t="s">
+        <v>90</v>
+      </c>
+      <c r="L4" t="s">
+        <v>87</v>
+      </c>
+      <c r="M4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P4" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" t="s">
+        <v>62</v>
+      </c>
+      <c r="S4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T4" t="s">
+        <v>5</v>
+      </c>
+      <c r="U4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>53</v>
+      </c>
+      <c r="X4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
+        <v>45</v>
+      </c>
+      <c r="O5" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>46</v>
+      </c>
+      <c r="R5" t="s">
+        <v>62</v>
+      </c>
+      <c r="S5" t="s">
+        <v>6</v>
+      </c>
+      <c r="T5" t="s">
+        <v>5</v>
+      </c>
+      <c r="U5" t="s">
+        <v>52</v>
+      </c>
+      <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK5" s="4"/>
+      <c r="AM5" s="3"/>
+      <c r="AO5" s="3"/>
+      <c r="AP5" s="3"/>
+      <c r="AR5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX5">
+        <v>100</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ5">
+        <v>25</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB5">
+        <v>20</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD5">
+        <v>20</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" t="s">
+        <v>45</v>
+      </c>
+      <c r="O6" t="s">
+        <v>6</v>
+      </c>
+      <c r="P6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>46</v>
+      </c>
+      <c r="R6" t="s">
+        <v>62</v>
+      </c>
+      <c r="S6" t="s">
+        <v>6</v>
+      </c>
+      <c r="T6" t="s">
+        <v>5</v>
+      </c>
+      <c r="U6" t="s">
+        <v>52</v>
+      </c>
+      <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>53</v>
+      </c>
+      <c r="X6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK6" s="4"/>
+      <c r="AM6" s="3"/>
+      <c r="AO6" s="3"/>
+      <c r="AP6" s="3"/>
+      <c r="AR6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX6">
+        <v>100</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ6">
+        <v>25</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB6">
+        <v>20</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD6">
+        <v>20</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J7" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" t="s">
+        <v>89</v>
+      </c>
+      <c r="L7" t="s">
+        <v>86</v>
+      </c>
+      <c r="M7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O7" t="s">
+        <v>6</v>
+      </c>
+      <c r="P7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>46</v>
+      </c>
+      <c r="R7" t="s">
+        <v>62</v>
+      </c>
+      <c r="S7" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7" t="s">
+        <v>5</v>
+      </c>
+      <c r="U7" t="s">
+        <v>52</v>
+      </c>
+      <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>53</v>
+      </c>
+      <c r="X7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK7" s="4"/>
+      <c r="AM7" s="3"/>
+      <c r="AO7" s="3"/>
+      <c r="AP7" s="3"/>
+      <c r="AR7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX7">
+        <v>100</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ7">
+        <v>25</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB7">
+        <v>20</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD7">
+        <v>20</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" t="s">
+        <v>90</v>
+      </c>
+      <c r="L8" t="s">
+        <v>87</v>
+      </c>
+      <c r="M8" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P8" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>46</v>
+      </c>
+      <c r="R8" t="s">
+        <v>62</v>
+      </c>
+      <c r="S8" t="s">
+        <v>6</v>
+      </c>
+      <c r="T8" t="s">
+        <v>5</v>
+      </c>
+      <c r="U8" t="s">
+        <v>52</v>
+      </c>
+      <c r="V8" t="s">
+        <v>43</v>
+      </c>
+      <c r="W8" t="s">
+        <v>53</v>
+      </c>
+      <c r="X8" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" t="s">
+        <v>6</v>
+      </c>
+      <c r="P9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>46</v>
+      </c>
+      <c r="R9" t="s">
+        <v>62</v>
+      </c>
+      <c r="S9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" t="s">
+        <v>52</v>
+      </c>
+      <c r="V9" t="s">
+        <v>43</v>
+      </c>
+      <c r="W9" t="s">
+        <v>53</v>
+      </c>
+      <c r="X9" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="4"/>
+      <c r="AM9" s="3"/>
+      <c r="AO9" s="3"/>
+      <c r="AP9" s="3"/>
+      <c r="AR9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX9">
+        <v>100</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ9">
+        <v>25</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB9">
+        <v>20</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD9">
+        <v>20</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" t="s">
+        <v>43</v>
+      </c>
+      <c r="N10" t="s">
+        <v>45</v>
+      </c>
+      <c r="O10" t="s">
+        <v>6</v>
+      </c>
+      <c r="P10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>46</v>
+      </c>
+      <c r="R10" t="s">
+        <v>62</v>
+      </c>
+      <c r="S10" t="s">
+        <v>6</v>
+      </c>
+      <c r="T10" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" t="s">
+        <v>52</v>
+      </c>
+      <c r="V10" t="s">
+        <v>43</v>
+      </c>
+      <c r="W10" t="s">
+        <v>53</v>
+      </c>
+      <c r="X10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="4"/>
+      <c r="AM10" s="3"/>
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="3"/>
+      <c r="AR10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX10">
+        <v>100</v>
+      </c>
+      <c r="AY10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ10">
+        <v>25</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB10">
+        <v>20</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD10">
+        <v>20</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" t="s">
+        <v>101</v>
+      </c>
+      <c r="J11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" t="s">
+        <v>86</v>
+      </c>
+      <c r="M11" t="s">
+        <v>43</v>
+      </c>
+      <c r="N11" t="s">
+        <v>45</v>
+      </c>
+      <c r="O11" t="s">
+        <v>6</v>
+      </c>
+      <c r="P11" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>46</v>
+      </c>
+      <c r="R11" t="s">
+        <v>62</v>
+      </c>
+      <c r="S11" t="s">
+        <v>6</v>
+      </c>
+      <c r="T11" t="s">
+        <v>5</v>
+      </c>
+      <c r="U11" t="s">
+        <v>52</v>
+      </c>
+      <c r="V11" t="s">
+        <v>43</v>
+      </c>
+      <c r="W11" t="s">
+        <v>53</v>
+      </c>
+      <c r="X11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK11" s="4"/>
+      <c r="AM11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AR11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX11">
+        <v>100</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ11">
+        <v>25</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB11">
+        <v>20</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD11">
+        <v>20</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" t="s">
+        <v>6</v>
+      </c>
+      <c r="P12" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>46</v>
+      </c>
+      <c r="R12" t="s">
+        <v>62</v>
+      </c>
+      <c r="S12" t="s">
+        <v>6</v>
+      </c>
+      <c r="T12" t="s">
+        <v>5</v>
+      </c>
+      <c r="U12" t="s">
+        <v>52</v>
+      </c>
+      <c r="V12" t="s">
+        <v>43</v>
+      </c>
+      <c r="W12" t="s">
+        <v>53</v>
+      </c>
+      <c r="X12" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" t="s">
+        <v>101</v>
+      </c>
+      <c r="J13" t="s">
+        <v>102</v>
+      </c>
+      <c r="K13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L13" t="s">
+        <v>3</v>
+      </c>
+      <c r="M13" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" t="s">
+        <v>45</v>
+      </c>
+      <c r="O13" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>46</v>
+      </c>
+      <c r="R13" t="s">
+        <v>62</v>
+      </c>
+      <c r="S13" t="s">
+        <v>6</v>
+      </c>
+      <c r="T13" t="s">
+        <v>5</v>
+      </c>
+      <c r="U13" t="s">
+        <v>52</v>
+      </c>
+      <c r="V13" t="s">
+        <v>43</v>
+      </c>
+      <c r="W13" t="s">
+        <v>53</v>
+      </c>
+      <c r="X13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK13" s="4"/>
+      <c r="AM13" s="3"/>
+      <c r="AO13" s="3"/>
+      <c r="AP13" s="3"/>
+      <c r="AR13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX13">
+        <v>100</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ13">
+        <v>25</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB13">
+        <v>20</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD13">
+        <v>20</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L14" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" t="s">
+        <v>43</v>
+      </c>
+      <c r="N14" t="s">
+        <v>45</v>
+      </c>
+      <c r="O14" t="s">
+        <v>6</v>
+      </c>
+      <c r="P14" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>46</v>
+      </c>
+      <c r="R14" t="s">
+        <v>62</v>
+      </c>
+      <c r="S14" t="s">
+        <v>6</v>
+      </c>
+      <c r="T14" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" t="s">
+        <v>52</v>
+      </c>
+      <c r="V14" t="s">
+        <v>43</v>
+      </c>
+      <c r="W14" t="s">
+        <v>53</v>
+      </c>
+      <c r="X14" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK14" s="4"/>
+      <c r="AM14" s="3"/>
+      <c r="AO14" s="3"/>
+      <c r="AP14" s="3"/>
+      <c r="AR14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX14">
+        <v>100</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ14">
+        <v>25</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB14">
+        <v>20</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD14">
+        <v>20</v>
+      </c>
+      <c r="BE14" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" t="s">
+        <v>101</v>
+      </c>
+      <c r="J15" t="s">
+        <v>102</v>
+      </c>
+      <c r="K15" t="s">
+        <v>89</v>
+      </c>
+      <c r="L15" t="s">
+        <v>86</v>
+      </c>
+      <c r="M15" t="s">
+        <v>43</v>
+      </c>
+      <c r="N15" t="s">
+        <v>45</v>
+      </c>
+      <c r="O15" t="s">
+        <v>6</v>
+      </c>
+      <c r="P15" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>46</v>
+      </c>
+      <c r="R15" t="s">
+        <v>62</v>
+      </c>
+      <c r="S15" t="s">
+        <v>6</v>
+      </c>
+      <c r="T15" t="s">
+        <v>5</v>
+      </c>
+      <c r="U15" t="s">
+        <v>52</v>
+      </c>
+      <c r="V15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" t="s">
+        <v>53</v>
+      </c>
+      <c r="X15" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK15" s="4"/>
+      <c r="AM15" s="3"/>
+      <c r="AO15" s="3"/>
+      <c r="AP15" s="3"/>
+      <c r="AR15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX15">
+        <v>100</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ15">
+        <v>25</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB15">
+        <v>20</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD15">
+        <v>20</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" t="s">
+        <v>102</v>
+      </c>
+      <c r="K16" t="s">
+        <v>90</v>
+      </c>
+      <c r="L16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M16" t="s">
+        <v>43</v>
+      </c>
+      <c r="N16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O16" t="s">
+        <v>6</v>
+      </c>
+      <c r="P16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>46</v>
+      </c>
+      <c r="R16" t="s">
+        <v>62</v>
+      </c>
+      <c r="S16" t="s">
+        <v>6</v>
+      </c>
+      <c r="T16" t="s">
+        <v>5</v>
+      </c>
+      <c r="U16" t="s">
+        <v>52</v>
+      </c>
+      <c r="V16" t="s">
+        <v>43</v>
+      </c>
+      <c r="W16" t="s">
+        <v>53</v>
+      </c>
+      <c r="X16" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" t="s">
+        <v>112</v>
+      </c>
+      <c r="J17" t="s">
+        <v>102</v>
+      </c>
+      <c r="K17" t="s">
+        <v>40</v>
+      </c>
+      <c r="L17" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" t="s">
+        <v>43</v>
+      </c>
+      <c r="N17" t="s">
+        <v>45</v>
+      </c>
+      <c r="O17" t="s">
+        <v>6</v>
+      </c>
+      <c r="P17" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>46</v>
+      </c>
+      <c r="R17" t="s">
+        <v>62</v>
+      </c>
+      <c r="S17" t="s">
+        <v>6</v>
+      </c>
+      <c r="T17" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" t="s">
+        <v>52</v>
+      </c>
+      <c r="V17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W17" t="s">
+        <v>53</v>
+      </c>
+      <c r="X17" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK17" s="4"/>
+      <c r="AM17" s="3"/>
+      <c r="AO17" s="3"/>
+      <c r="AP17" s="3"/>
+      <c r="AR17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX17">
+        <v>100</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ17">
+        <v>25</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB17">
+        <v>20</v>
+      </c>
+      <c r="BC17" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD17">
+        <v>20</v>
+      </c>
+      <c r="BE17" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" t="s">
+        <v>112</v>
+      </c>
+      <c r="J18" t="s">
+        <v>102</v>
+      </c>
+      <c r="K18" t="s">
+        <v>88</v>
+      </c>
+      <c r="L18" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" t="s">
+        <v>43</v>
+      </c>
+      <c r="N18" t="s">
+        <v>45</v>
+      </c>
+      <c r="O18" t="s">
+        <v>6</v>
+      </c>
+      <c r="P18" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>46</v>
+      </c>
+      <c r="R18" t="s">
+        <v>62</v>
+      </c>
+      <c r="S18" t="s">
+        <v>6</v>
+      </c>
+      <c r="T18" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" t="s">
+        <v>52</v>
+      </c>
+      <c r="V18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W18" t="s">
+        <v>53</v>
+      </c>
+      <c r="X18" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK18" s="4"/>
+      <c r="AM18" s="3"/>
+      <c r="AO18" s="3"/>
+      <c r="AP18" s="3"/>
+      <c r="AR18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX18">
+        <v>100</v>
+      </c>
+      <c r="AY18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ18">
+        <v>25</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB18">
+        <v>20</v>
+      </c>
+      <c r="BC18" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD18">
+        <v>20</v>
+      </c>
+      <c r="BE18" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" t="s">
+        <v>112</v>
+      </c>
+      <c r="J19" t="s">
+        <v>102</v>
+      </c>
+      <c r="K19" t="s">
+        <v>89</v>
+      </c>
+      <c r="L19" t="s">
+        <v>86</v>
+      </c>
+      <c r="M19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N19" t="s">
+        <v>45</v>
+      </c>
+      <c r="O19" t="s">
+        <v>6</v>
+      </c>
+      <c r="P19" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>46</v>
+      </c>
+      <c r="R19" t="s">
+        <v>62</v>
+      </c>
+      <c r="S19" t="s">
+        <v>6</v>
+      </c>
+      <c r="T19" t="s">
+        <v>5</v>
+      </c>
+      <c r="U19" t="s">
+        <v>52</v>
+      </c>
+      <c r="V19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W19" t="s">
+        <v>53</v>
+      </c>
+      <c r="X19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK19" s="4"/>
+      <c r="AM19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AR19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX19">
+        <v>100</v>
+      </c>
+      <c r="AY19" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ19">
+        <v>25</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB19">
+        <v>20</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD19">
+        <v>20</v>
+      </c>
+      <c r="BE19" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" t="s">
+        <v>112</v>
+      </c>
+      <c r="J20" t="s">
+        <v>102</v>
+      </c>
+      <c r="K20" t="s">
+        <v>90</v>
+      </c>
+      <c r="L20" t="s">
+        <v>87</v>
+      </c>
+      <c r="M20" t="s">
+        <v>43</v>
+      </c>
+      <c r="N20" t="s">
+        <v>45</v>
+      </c>
+      <c r="O20" t="s">
+        <v>6</v>
+      </c>
+      <c r="P20" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R20" t="s">
+        <v>62</v>
+      </c>
+      <c r="S20" t="s">
+        <v>6</v>
+      </c>
+      <c r="T20" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" t="s">
+        <v>52</v>
+      </c>
+      <c r="V20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" t="s">
+        <v>53</v>
+      </c>
+      <c r="X20" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" t="s">
+        <v>111</v>
+      </c>
+      <c r="K21" t="s">
+        <v>40</v>
+      </c>
+      <c r="L21" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N21" t="s">
+        <v>45</v>
+      </c>
+      <c r="O21" t="s">
+        <v>6</v>
+      </c>
+      <c r="P21" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>46</v>
+      </c>
+      <c r="R21" t="s">
+        <v>62</v>
+      </c>
+      <c r="S21" t="s">
+        <v>6</v>
+      </c>
+      <c r="T21" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" t="s">
+        <v>52</v>
+      </c>
+      <c r="V21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" t="s">
+        <v>53</v>
+      </c>
+      <c r="X21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="4"/>
+      <c r="AM21" s="3"/>
+      <c r="AO21" s="3"/>
+      <c r="AP21" s="3"/>
+      <c r="AR21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX21">
+        <v>100</v>
+      </c>
+      <c r="AY21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ21">
+        <v>25</v>
+      </c>
+      <c r="BA21" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB21">
+        <v>20</v>
+      </c>
+      <c r="BC21" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD21">
+        <v>20</v>
+      </c>
+      <c r="BE21" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" t="s">
+        <v>112</v>
+      </c>
+      <c r="J22" t="s">
+        <v>111</v>
+      </c>
+      <c r="K22" t="s">
+        <v>88</v>
+      </c>
+      <c r="L22" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N22" t="s">
+        <v>45</v>
+      </c>
+      <c r="O22" t="s">
+        <v>6</v>
+      </c>
+      <c r="P22" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R22" t="s">
+        <v>62</v>
+      </c>
+      <c r="S22" t="s">
+        <v>6</v>
+      </c>
+      <c r="T22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" t="s">
+        <v>52</v>
+      </c>
+      <c r="V22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W22" t="s">
+        <v>53</v>
+      </c>
+      <c r="X22" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK22" s="4"/>
+      <c r="AM22" s="3"/>
+      <c r="AO22" s="3"/>
+      <c r="AP22" s="3"/>
+      <c r="AR22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS22" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT22" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW22" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX22">
+        <v>100</v>
+      </c>
+      <c r="AY22" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ22">
+        <v>25</v>
+      </c>
+      <c r="BA22" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB22">
+        <v>20</v>
+      </c>
+      <c r="BC22" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD22">
+        <v>20</v>
+      </c>
+      <c r="BE22" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" t="s">
+        <v>112</v>
+      </c>
+      <c r="J23" t="s">
+        <v>111</v>
+      </c>
+      <c r="K23" t="s">
+        <v>89</v>
+      </c>
+      <c r="L23" t="s">
+        <v>86</v>
+      </c>
+      <c r="M23" t="s">
+        <v>43</v>
+      </c>
+      <c r="N23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O23" t="s">
+        <v>6</v>
+      </c>
+      <c r="P23" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R23" t="s">
+        <v>62</v>
+      </c>
+      <c r="S23" t="s">
+        <v>6</v>
+      </c>
+      <c r="T23" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" t="s">
+        <v>52</v>
+      </c>
+      <c r="V23" t="s">
+        <v>43</v>
+      </c>
+      <c r="W23" t="s">
+        <v>53</v>
+      </c>
+      <c r="X23" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK23" s="4"/>
+      <c r="AM23" s="3"/>
+      <c r="AO23" s="3"/>
+      <c r="AP23" s="3"/>
+      <c r="AR23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW23" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX23">
+        <v>100</v>
+      </c>
+      <c r="AY23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ23">
+        <v>25</v>
+      </c>
+      <c r="BA23" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB23">
+        <v>20</v>
+      </c>
+      <c r="BC23" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD23">
+        <v>20</v>
+      </c>
+      <c r="BE23" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" t="s">
+        <v>112</v>
+      </c>
+      <c r="J24" t="s">
+        <v>111</v>
+      </c>
+      <c r="K24" t="s">
+        <v>90</v>
+      </c>
+      <c r="L24" t="s">
+        <v>87</v>
+      </c>
+      <c r="M24" t="s">
+        <v>43</v>
+      </c>
+      <c r="N24" t="s">
+        <v>45</v>
+      </c>
+      <c r="O24" t="s">
+        <v>6</v>
+      </c>
+      <c r="P24" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>46</v>
+      </c>
+      <c r="R24" t="s">
+        <v>62</v>
+      </c>
+      <c r="S24" t="s">
+        <v>6</v>
+      </c>
+      <c r="T24" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" t="s">
+        <v>52</v>
+      </c>
+      <c r="V24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>53</v>
+      </c>
+      <c r="X24" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BY1:BY24" xr:uid="{DC9C344B-BDE6-4A60-B8FB-2D4AAF4F3344}">
+      <formula1>"Intervención Psicosocial,Tratamiento Farmacológico,Ambos,No Aplica"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="B5:B8" r:id="rId1" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{20A6198B-F417-40A8-8627-8668F560453D}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{33736C83-7E2A-4A90-9642-EA8B66327004}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{694169EE-5731-4358-94B1-4A45CE7CF1F2}"/>
+    <hyperlink ref="B6:B8" r:id="rId4" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{08551A9D-3F12-468F-A6B4-E4CC71F9AAE3}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{DDF8E31A-CBA3-4CA4-84E0-BAB944823E35}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{BFE70029-719A-4A66-AA8C-601CDAF85BB2}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{6DC83D43-81D3-4679-A819-D107E8AFFD5A}"/>
+    <hyperlink ref="B1" r:id="rId8" xr:uid="{8D346009-13BF-40A9-A873-46AE105E0BB3}"/>
+    <hyperlink ref="D1" r:id="rId9" xr:uid="{A86FB013-E363-4C0E-B7E8-2F180AC376D3}"/>
+    <hyperlink ref="D2" r:id="rId10" xr:uid="{6AC40481-6564-457B-AFF8-03D60A0E2A3E}"/>
+    <hyperlink ref="D3" r:id="rId11" xr:uid="{4A97FE31-C8B6-4D6C-80CB-2C3FFF3779BE}"/>
+    <hyperlink ref="D4" r:id="rId12" xr:uid="{7A504388-E6B6-4965-8C3E-5069DC4AE63E}"/>
+    <hyperlink ref="B13:B16" r:id="rId13" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{FB366572-567F-46A4-B130-0A9F448F53EB}"/>
+    <hyperlink ref="B13" r:id="rId14" xr:uid="{B7D75009-FE2A-4F52-825E-D16674ED2C18}"/>
+    <hyperlink ref="D13" r:id="rId15" xr:uid="{9F5D899A-90CA-462F-A123-DE8FF6ADA3AF}"/>
+    <hyperlink ref="B14:B16" r:id="rId16" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{503CD5EA-A59B-4657-AF78-E8EDFCEB3C7D}"/>
+    <hyperlink ref="D14" r:id="rId17" xr:uid="{C10065F1-A661-4718-AC02-1E3C04DEB43B}"/>
+    <hyperlink ref="D15" r:id="rId18" xr:uid="{A27C6F4D-6087-448A-A2B6-A656F9B401D0}"/>
+    <hyperlink ref="D16" r:id="rId19" xr:uid="{5490F5B0-B9FA-4EDF-BE9A-8534DEE273F1}"/>
+    <hyperlink ref="B9" r:id="rId20" xr:uid="{8BF6DE7B-784D-436B-84CD-8E0BDFC5D95F}"/>
+    <hyperlink ref="D9" r:id="rId21" xr:uid="{1C2AB6D8-0E19-4FFB-824C-3DCA679C066D}"/>
+    <hyperlink ref="D10" r:id="rId22" xr:uid="{F10AC502-37F1-4BB0-A68E-C196D526AECC}"/>
+    <hyperlink ref="D11" r:id="rId23" xr:uid="{FF0CCA05-15B2-4F7E-BE07-58AD34A386F9}"/>
+    <hyperlink ref="D12" r:id="rId24" xr:uid="{1B62D41E-E8C4-43CC-B4A6-131682ECCC91}"/>
+    <hyperlink ref="B21:B24" r:id="rId25" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{AB2BF27A-9A89-4139-849D-536F0F2D0F65}"/>
+    <hyperlink ref="B21" r:id="rId26" xr:uid="{195118D5-492D-45AB-A9BB-00B625F83014}"/>
+    <hyperlink ref="D21" r:id="rId27" xr:uid="{D05EC650-1ADB-40A9-8BAB-AB68CD9207FF}"/>
+    <hyperlink ref="B22:B24" r:id="rId28" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{DF6EBDA2-5C33-417A-A0CF-87058027C43A}"/>
+    <hyperlink ref="D22" r:id="rId29" xr:uid="{BD092C6F-EA87-473B-A25D-A9FEE2659DBC}"/>
+    <hyperlink ref="D23" r:id="rId30" xr:uid="{5BC6C16E-C9C8-43F3-949E-1A5655A8F29C}"/>
+    <hyperlink ref="D24" r:id="rId31" xr:uid="{7D2902C0-9E4E-4362-A806-3694D9F105A6}"/>
+    <hyperlink ref="B17" r:id="rId32" xr:uid="{C50F52EB-0927-4BD7-A8A7-8404907C67F5}"/>
+    <hyperlink ref="D17" r:id="rId33" xr:uid="{23AEE11B-7EC0-45F5-9FCA-CEE9A29F1D3D}"/>
+    <hyperlink ref="D18" r:id="rId34" xr:uid="{D3A2FD01-F010-4D3A-AAE0-B3CEB9EEF1C3}"/>
+    <hyperlink ref="D19" r:id="rId35" xr:uid="{2EB6034D-1D7F-416A-A1BD-FBA3DA2D4A23}"/>
+    <hyperlink ref="D20" r:id="rId36" xr:uid="{A25451EE-8204-44B5-99A4-957D06A93504}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/datos/SuitePruebas.xlsx
+++ b/src/datos/SuitePruebas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\AutomatizacionAF\src\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automatización\Git\AutomatizacionAF\src\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A155A4FD-CB18-4AB7-A46C-1480329278F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3E2163-F863-4752-A213-E0BB383AFBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-156" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CotizadorAF" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="122">
   <si>
     <t>EscenarioPrueba</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>Cotizacion Optima Plus Mensual</t>
+  </si>
+  <si>
+    <t>$2,000.00 / $4,000.00 USD</t>
   </si>
 </sst>
 </file>
@@ -470,7 +473,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -480,7 +483,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1084,7 +1086,7 @@
       </c>
     </row>
     <row r="2" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" t="s">
         <v>103</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1187,7 +1189,7 @@
         <v>6</v>
       </c>
       <c r="AI2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK2" s="4"/>
       <c r="AM2" s="3"/>
@@ -1240,7 +1242,7 @@
       </c>
     </row>
     <row r="3" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" t="s">
         <v>104</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1271,7 +1273,7 @@
         <v>102</v>
       </c>
       <c r="K3" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="L3" t="s">
         <v>4</v>
@@ -1343,7 +1345,7 @@
         <v>6</v>
       </c>
       <c r="AI3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK3" s="4"/>
       <c r="AM3" s="3"/>
@@ -1396,7 +1398,7 @@
       </c>
     </row>
     <row r="4" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" t="s">
         <v>105</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1499,7 +1501,7 @@
         <v>6</v>
       </c>
       <c r="AI4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK4" s="4"/>
       <c r="AM4" s="3"/>
@@ -1552,7 +1554,7 @@
       </c>
     </row>
     <row r="5" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" t="s">
         <v>106</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1655,11 +1657,11 @@
         <v>6</v>
       </c>
       <c r="AI5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" t="s">
         <v>107</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1762,7 +1764,7 @@
         <v>6</v>
       </c>
       <c r="AI6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK6" s="4"/>
       <c r="AM6" s="3"/>
@@ -1815,7 +1817,7 @@
       </c>
     </row>
     <row r="7" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" t="s">
         <v>108</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1846,7 +1848,7 @@
         <v>111</v>
       </c>
       <c r="K7" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s">
         <v>4</v>
@@ -1918,7 +1920,7 @@
         <v>6</v>
       </c>
       <c r="AI7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK7" s="4"/>
       <c r="AM7" s="3"/>
@@ -1971,7 +1973,7 @@
       </c>
     </row>
     <row r="8" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" t="s">
         <v>109</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -2074,7 +2076,7 @@
         <v>6</v>
       </c>
       <c r="AI8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK8" s="4"/>
       <c r="AM8" s="3"/>
@@ -2127,7 +2129,7 @@
       </c>
     </row>
     <row r="9" spans="1:117" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" t="s">
         <v>110</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -2230,7 +2232,7 @@
         <v>6</v>
       </c>
       <c r="AI9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:117" x14ac:dyDescent="0.25">

--- a/src/datos/SuitePruebas.xlsx
+++ b/src/datos/SuitePruebas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automatización\Git\AutomatizacionAF\src\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diegobautistaluis/Git/AutomatizacionAF/src/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3E2163-F863-4752-A213-E0BB383AFBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE40AE5-7D73-164A-A5CC-C5351225B310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CotizadorAF" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="122">
   <si>
     <t>EscenarioPrueba</t>
   </si>
@@ -820,120 +820,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DM13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="23" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="23.42578125" customWidth="1"/>
-    <col min="28" max="28" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="23.5" customWidth="1"/>
+    <col min="28" max="28" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="25" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="26" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="14" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="27.28515625" customWidth="1"/>
-    <col min="60" max="60" width="17.28515625" customWidth="1"/>
-    <col min="61" max="61" width="21.140625" customWidth="1"/>
-    <col min="62" max="62" width="11.7109375" customWidth="1"/>
+    <col min="54" max="54" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="27.33203125" customWidth="1"/>
+    <col min="60" max="60" width="17.33203125" customWidth="1"/>
+    <col min="61" max="61" width="21.1640625" customWidth="1"/>
+    <col min="62" max="62" width="11.6640625" customWidth="1"/>
     <col min="63" max="63" width="17" customWidth="1"/>
-    <col min="65" max="65" width="11.7109375" customWidth="1"/>
-    <col min="66" max="66" width="16.140625" customWidth="1"/>
-    <col min="67" max="67" width="19.140625" customWidth="1"/>
-    <col min="68" max="68" width="22.7109375" customWidth="1"/>
-    <col min="69" max="69" width="20.7109375" customWidth="1"/>
-    <col min="70" max="70" width="13.28515625" customWidth="1"/>
+    <col min="65" max="65" width="11.6640625" customWidth="1"/>
+    <col min="66" max="66" width="16.1640625" customWidth="1"/>
+    <col min="67" max="67" width="19.1640625" customWidth="1"/>
+    <col min="68" max="68" width="22.6640625" customWidth="1"/>
+    <col min="69" max="69" width="20.6640625" customWidth="1"/>
+    <col min="70" max="70" width="13.33203125" customWidth="1"/>
     <col min="71" max="71" width="15" customWidth="1"/>
-    <col min="74" max="74" width="27.7109375" customWidth="1"/>
-    <col min="75" max="75" width="14.42578125" customWidth="1"/>
-    <col min="76" max="76" width="20.42578125" customWidth="1"/>
-    <col min="77" max="77" width="22.140625" customWidth="1"/>
-    <col min="78" max="78" width="26.7109375" customWidth="1"/>
-    <col min="79" max="79" width="28.85546875" customWidth="1"/>
-    <col min="80" max="80" width="13.7109375" customWidth="1"/>
-    <col min="81" max="81" width="22.85546875" customWidth="1"/>
-    <col min="82" max="82" width="20.7109375" customWidth="1"/>
-    <col min="83" max="83" width="23.28515625" customWidth="1"/>
-    <col min="84" max="84" width="31.140625" customWidth="1"/>
-    <col min="85" max="85" width="26.42578125" customWidth="1"/>
-    <col min="86" max="86" width="23.7109375" customWidth="1"/>
-    <col min="87" max="87" width="17.28515625" customWidth="1"/>
-    <col min="88" max="88" width="19.28515625" customWidth="1"/>
-    <col min="89" max="89" width="19.42578125" customWidth="1"/>
-    <col min="90" max="90" width="17.140625" customWidth="1"/>
-    <col min="91" max="91" width="17.7109375" customWidth="1"/>
-    <col min="92" max="92" width="14.7109375" customWidth="1"/>
-    <col min="93" max="93" width="26.7109375" customWidth="1"/>
-    <col min="94" max="94" width="27.42578125" customWidth="1"/>
-    <col min="95" max="95" width="17.140625" customWidth="1"/>
-    <col min="96" max="96" width="17.85546875" customWidth="1"/>
+    <col min="74" max="74" width="27.6640625" customWidth="1"/>
+    <col min="75" max="75" width="14.5" customWidth="1"/>
+    <col min="76" max="76" width="20.5" customWidth="1"/>
+    <col min="77" max="77" width="22.1640625" customWidth="1"/>
+    <col min="78" max="78" width="26.6640625" customWidth="1"/>
+    <col min="79" max="79" width="28.83203125" customWidth="1"/>
+    <col min="80" max="80" width="13.6640625" customWidth="1"/>
+    <col min="81" max="81" width="22.83203125" customWidth="1"/>
+    <col min="82" max="82" width="20.6640625" customWidth="1"/>
+    <col min="83" max="83" width="23.33203125" customWidth="1"/>
+    <col min="84" max="84" width="31.1640625" customWidth="1"/>
+    <col min="85" max="85" width="26.5" customWidth="1"/>
+    <col min="86" max="86" width="23.6640625" customWidth="1"/>
+    <col min="87" max="87" width="17.33203125" customWidth="1"/>
+    <col min="88" max="88" width="19.33203125" customWidth="1"/>
+    <col min="89" max="89" width="19.5" customWidth="1"/>
+    <col min="90" max="90" width="17.1640625" customWidth="1"/>
+    <col min="91" max="91" width="17.6640625" customWidth="1"/>
+    <col min="92" max="92" width="14.6640625" customWidth="1"/>
+    <col min="93" max="93" width="26.6640625" customWidth="1"/>
+    <col min="94" max="94" width="27.5" customWidth="1"/>
+    <col min="95" max="95" width="17.1640625" customWidth="1"/>
+    <col min="96" max="96" width="17.83203125" customWidth="1"/>
     <col min="97" max="97" width="19" customWidth="1"/>
     <col min="98" max="99" width="29" customWidth="1"/>
-    <col min="100" max="100" width="17.28515625" customWidth="1"/>
+    <col min="100" max="100" width="17.33203125" customWidth="1"/>
     <col min="101" max="101" width="20" customWidth="1"/>
-    <col min="102" max="102" width="17.7109375" customWidth="1"/>
-    <col min="103" max="107" width="20.5703125" customWidth="1"/>
+    <col min="102" max="102" width="17.6640625" customWidth="1"/>
+    <col min="103" max="107" width="20.5" customWidth="1"/>
     <col min="108" max="108" width="14" customWidth="1"/>
     <col min="109" max="109" width="15" customWidth="1"/>
-    <col min="110" max="110" width="19.28515625" customWidth="1"/>
-    <col min="111" max="111" width="13.85546875" customWidth="1"/>
-    <col min="112" max="112" width="21.7109375" customWidth="1"/>
+    <col min="110" max="110" width="19.33203125" customWidth="1"/>
+    <col min="111" max="111" width="13.83203125" customWidth="1"/>
+    <col min="112" max="112" width="21.6640625" customWidth="1"/>
     <col min="113" max="113" width="24" customWidth="1"/>
-    <col min="114" max="114" width="18.140625" customWidth="1"/>
-    <col min="115" max="115" width="21.28515625" customWidth="1"/>
-    <col min="116" max="116" width="22.5703125" customWidth="1"/>
-    <col min="117" max="117" width="14.85546875" customWidth="1"/>
+    <col min="114" max="114" width="18.1640625" customWidth="1"/>
+    <col min="115" max="115" width="21.33203125" customWidth="1"/>
+    <col min="116" max="116" width="22.5" customWidth="1"/>
+    <col min="117" max="117" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1085,9 +1085,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
@@ -1111,13 +1111,13 @@
         <v>35</v>
       </c>
       <c r="I2" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J2" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="K2" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="L2" t="s">
         <v>3</v>
@@ -1241,7 +1241,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>106</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>107</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>108</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>109</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -2235,20 +2235,20 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:117" x14ac:dyDescent="0.2">
       <c r="AU10" s="2"/>
       <c r="DM10" s="2"/>
     </row>
-    <row r="11" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:117" x14ac:dyDescent="0.2">
       <c r="G11" t="s">
         <v>42</v>
       </c>
       <c r="AU11" s="2"/>
     </row>
-    <row r="12" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:117" x14ac:dyDescent="0.2">
       <c r="BE12" s="1"/>
     </row>
-    <row r="13" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:117" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
         <v>24</v>
       </c>
@@ -2282,16 +2282,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91658F97-1B63-4028-A047-57A0079160D2}">
   <dimension ref="A1:AE4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="23.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="54.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="11.42578125" style="4"/>
+    <col min="1" max="2" width="23.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="11.5" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:31" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>77</v>
       </c>
@@ -2327,10 +2327,10 @@
       </c>
       <c r="AE2" s="5"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE3" s="5"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE4" s="5"/>
     </row>
   </sheetData>
@@ -2345,12 +2345,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89217B83-F5AC-41B7-85ED-07DFA2DFDFF5}">
   <dimension ref="A1:BF24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34.5703125" customWidth="1"/>
+    <col min="1" max="1" width="34.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>114</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>113</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>92</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>93</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>94</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>95</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>96</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>115</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>97</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>98</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>99</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>100</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>117</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>118</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>119</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>120</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>103</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>104</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>105</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>106</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>107</v>
       </c>
@@ -5381,7 +5381,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>108</v>
       </c>
@@ -5537,7 +5537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>109</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>110</v>
       </c>

--- a/src/datos/SuitePruebas.xlsx
+++ b/src/datos/SuitePruebas.xlsx
@@ -1,339 +1,371 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diegobautistaluis/Git/AutomatizacionAF/src/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE40AE5-7D73-164A-A5CC-C5351225B310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ABB099E-382C-7A4E-8851-39063FE56CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CotizadorAF" sheetId="1" r:id="rId1"/>
     <sheet name="EmisionAF" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja1" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="125">
   <si>
     <t>EscenarioPrueba</t>
   </si>
   <si>
+    <t>Url</t>
+  </si>
+  <si>
+    <t>IdiomaCotizacion</t>
+  </si>
+  <si>
+    <t>CorreoInicio</t>
+  </si>
+  <si>
+    <t>Contrasena</t>
+  </si>
+  <si>
+    <t>TipoPoliza</t>
+  </si>
+  <si>
+    <t>ConyugePareja</t>
+  </si>
+  <si>
+    <t>HijosMenoresDe24</t>
+  </si>
+  <si>
+    <t>CotizarPlan</t>
+  </si>
+  <si>
+    <t>RedProveedores</t>
+  </si>
+  <si>
+    <t>Deducible</t>
+  </si>
+  <si>
+    <t>FrecuenciaPago</t>
+  </si>
+  <si>
+    <t>SexoAlNacer</t>
+  </si>
+  <si>
     <t>EstadoCivil</t>
   </si>
   <si>
+    <t>TelefonoSecundario</t>
+  </si>
+  <si>
+    <t>EliminarTelSec</t>
+  </si>
+  <si>
+    <t>OcupacionTitular</t>
+  </si>
+  <si>
+    <t>TipoIdentificacionTitular</t>
+  </si>
+  <si>
+    <t>DireccionCorrespondencia</t>
+  </si>
+  <si>
+    <t>EliminarDirCorr</t>
+  </si>
+  <si>
+    <t>Hijo1</t>
+  </si>
+  <si>
+    <t>SexoDependiente1</t>
+  </si>
+  <si>
+    <t>Hijo2</t>
+  </si>
+  <si>
+    <t>SexoDependiente2</t>
+  </si>
+  <si>
+    <t>Hijo3</t>
+  </si>
+  <si>
+    <t>SexoDependiente3</t>
+  </si>
+  <si>
+    <t>Hijo4</t>
+  </si>
+  <si>
+    <t>SexoDependiente4</t>
+  </si>
+  <si>
+    <t>Hijo5</t>
+  </si>
+  <si>
+    <t>SexoDependiente5</t>
+  </si>
+  <si>
+    <t>RelacionSolicitantePrimario</t>
+  </si>
+  <si>
+    <t>CuestionarioMedicoCaptura</t>
+  </si>
+  <si>
+    <t>P5Sustancia</t>
+  </si>
+  <si>
+    <t>SigueIngiriendo</t>
+  </si>
+  <si>
+    <t>CapturaPreguntasPt2</t>
+  </si>
+  <si>
+    <t>EsquemaSumaInfarto</t>
+  </si>
+  <si>
+    <t>PeriodoPago</t>
+  </si>
+  <si>
+    <t>Factura</t>
+  </si>
+  <si>
+    <t>EstadoNacimiento</t>
+  </si>
+  <si>
+    <t>Beneficiario1</t>
+  </si>
+  <si>
+    <t>ProcentajeBen1</t>
+  </si>
+  <si>
+    <t>Beneficiario2</t>
+  </si>
+  <si>
+    <t>ProcentajeBen2</t>
+  </si>
+  <si>
+    <t>Beneficiario3</t>
+  </si>
+  <si>
+    <t>ProcentajeBen3</t>
+  </si>
+  <si>
+    <t>Beneficiario4</t>
+  </si>
+  <si>
+    <t>ProcentajeBen4</t>
+  </si>
+  <si>
+    <t>Beneficiario5</t>
+  </si>
+  <si>
+    <t>ProcentajeBen5</t>
+  </si>
+  <si>
+    <t>Cotizacion Optima Plus Anual</t>
+  </si>
+  <si>
+    <t>https://weeqp.azurewebsites.net/AF/Broker/Login/Auth</t>
+  </si>
+  <si>
+    <t>Eng</t>
+  </si>
+  <si>
+    <t>qahomxj1broker@yopmail.com</t>
+  </si>
+  <si>
+    <t>$Pass.01</t>
+  </si>
+  <si>
+    <t>Familiar</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>3+</t>
+  </si>
+  <si>
+    <t>Superior</t>
+  </si>
+  <si>
+    <t>Ultra</t>
+  </si>
+  <si>
+    <t>$5,000.00 / $5,000.00 USD</t>
+  </si>
+  <si>
+    <t>Anual</t>
+  </si>
+  <si>
+    <t>Masculino</t>
+  </si>
+  <si>
+    <t>Soltero(a)</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>Arte/Entretenimiento/Medios</t>
+  </si>
+  <si>
+    <t>ID del país</t>
+  </si>
+  <si>
+    <t>Hijo Biológico</t>
+  </si>
+  <si>
+    <t>Hijastro</t>
+  </si>
+  <si>
+    <t>Femenino</t>
+  </si>
+  <si>
+    <t>Hijo Adoptado Legalmente</t>
+  </si>
+  <si>
+    <t>Menor Bajo Custodia Legal</t>
+  </si>
+  <si>
+    <t>Cónyuge/Pareja Doméstica</t>
+  </si>
+  <si>
+    <t>Productos de Nicotina</t>
+  </si>
+  <si>
     <t>$10,000.00 MXN</t>
   </si>
   <si>
-    <t>Anual</t>
+    <t>Aguascalientes</t>
+  </si>
+  <si>
+    <t>Casado(a)</t>
+  </si>
+  <si>
+    <t>Cotizacion  Vital Plus Semestral</t>
+  </si>
+  <si>
+    <t>Esp</t>
+  </si>
+  <si>
+    <t>Vital</t>
+  </si>
+  <si>
+    <t>Plus</t>
+  </si>
+  <si>
+    <t>$2,000.00 / $4,000.00 USD</t>
   </si>
   <si>
     <t>Semestral</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Si</t>
-  </si>
-  <si>
-    <t>Aguascalientes</t>
-  </si>
-  <si>
-    <t>Casado(a)</t>
-  </si>
-  <si>
-    <t>EstadoNacimiento</t>
-  </si>
-  <si>
-    <t>PeriodoPago</t>
-  </si>
-  <si>
-    <t>Factura</t>
-  </si>
-  <si>
-    <t>Familiar</t>
-  </si>
-  <si>
-    <t>EsquemaSumaInfarto</t>
-  </si>
-  <si>
-    <t>Beneficiario1</t>
-  </si>
-  <si>
-    <t>Beneficiario2</t>
-  </si>
-  <si>
-    <t>Beneficiario5</t>
-  </si>
-  <si>
-    <t>Beneficiario4</t>
-  </si>
-  <si>
-    <t>Beneficiario3</t>
-  </si>
-  <si>
-    <t>ProcentajeBen1</t>
-  </si>
-  <si>
-    <t>ProcentajeBen2</t>
-  </si>
-  <si>
-    <t>ProcentajeBen3</t>
-  </si>
-  <si>
-    <t>ProcentajeBen4</t>
-  </si>
-  <si>
-    <t>ProcentajeBen5</t>
+    <t>Cotizacion  Vital Plus Trimestral</t>
+  </si>
+  <si>
+    <t>Trimestral</t>
+  </si>
+  <si>
+    <t>Cotizacion  Vital Plus Mensual</t>
+  </si>
+  <si>
+    <t>$5,000.00 / $7,500.00 USD</t>
+  </si>
+  <si>
+    <t>Mensual</t>
+  </si>
+  <si>
+    <t>Cotizacion Vital Core Anual</t>
+  </si>
+  <si>
+    <t>Core</t>
+  </si>
+  <si>
+    <t>$1,000.00 / $3,000.00 USD</t>
+  </si>
+  <si>
+    <t>Cotizacion Vital Core Semestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Vital Core Trimestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Vital Core Mensual</t>
   </si>
   <si>
     <t>`</t>
   </si>
   <si>
-    <t>Url</t>
-  </si>
-  <si>
-    <t>https://weeqp.azurewebsites.net/AF/Broker/Login/Auth</t>
-  </si>
-  <si>
-    <t>CorreoInicio</t>
-  </si>
-  <si>
-    <t>Contrasena</t>
-  </si>
-  <si>
-    <t>IdiomaCotizacion</t>
-  </si>
-  <si>
-    <t>Esp</t>
-  </si>
-  <si>
-    <t>$Pass.01</t>
-  </si>
-  <si>
-    <t>TipoPoliza</t>
-  </si>
-  <si>
-    <t>ConyugePareja</t>
-  </si>
-  <si>
-    <t>HijosMenoresDe24</t>
-  </si>
-  <si>
-    <t>3+</t>
-  </si>
-  <si>
-    <t>CotizarPlan</t>
-  </si>
-  <si>
-    <t>FrecuenciaPago</t>
-  </si>
-  <si>
-    <t>RedProveedores</t>
-  </si>
-  <si>
-    <t>Deducible</t>
-  </si>
-  <si>
-    <t>$1,000.00 / $3,000.00 USD</t>
-  </si>
-  <si>
-    <t>Ultra</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Masculino</t>
-  </si>
-  <si>
-    <t>Femenino</t>
-  </si>
-  <si>
-    <t>Soltero(a)</t>
-  </si>
-  <si>
-    <t>Arte/Entretenimiento/Medios</t>
-  </si>
-  <si>
-    <t>Hijo1</t>
-  </si>
-  <si>
-    <t>Hijo2</t>
-  </si>
-  <si>
-    <t>Hijo3</t>
-  </si>
-  <si>
-    <t>Hijo4</t>
-  </si>
-  <si>
-    <t>Hijo5</t>
-  </si>
-  <si>
-    <t>Hijo Biológico</t>
-  </si>
-  <si>
-    <t>Hijastro</t>
-  </si>
-  <si>
-    <t>Hijo Adoptado Legalmente</t>
-  </si>
-  <si>
-    <t>Menor Bajo Custodia Legal</t>
-  </si>
-  <si>
-    <t>Cónyuge/Pareja Doméstica</t>
-  </si>
-  <si>
-    <t>SexoAlNacer</t>
-  </si>
-  <si>
-    <t>TelefonoSecundario</t>
-  </si>
-  <si>
-    <t>EliminarTelSec</t>
-  </si>
-  <si>
-    <t>OcupacionTitular</t>
-  </si>
-  <si>
-    <t>TipoIdentificacionTitular</t>
-  </si>
-  <si>
-    <t>ID del país</t>
-  </si>
-  <si>
-    <t>DireccionCorrespondencia</t>
-  </si>
-  <si>
-    <t>EliminarDirCorr</t>
-  </si>
-  <si>
-    <t>SexoDependiente1</t>
-  </si>
-  <si>
-    <t>SexoDependiente2</t>
-  </si>
-  <si>
-    <t>SexoDependiente3</t>
-  </si>
-  <si>
-    <t>SexoDependiente4</t>
-  </si>
-  <si>
-    <t>SexoDependiente5</t>
-  </si>
-  <si>
-    <t>RelacionSolicitantePrimario</t>
-  </si>
-  <si>
-    <t>P5Sustancia</t>
-  </si>
-  <si>
-    <t>Productos de Nicotina</t>
-  </si>
-  <si>
-    <t>SigueIngiriendo</t>
-  </si>
-  <si>
-    <t>CuestionarioMedicoCaptura</t>
+    <t>CorreoClaims</t>
+  </si>
+  <si>
+    <t>ContrasenaClaims</t>
+  </si>
+  <si>
+    <t>UrlClaims</t>
+  </si>
+  <si>
+    <t>FolioSolicitante</t>
+  </si>
+  <si>
+    <t>Emision 1</t>
+  </si>
+  <si>
+    <t>pruebasxj@yopmail.com</t>
   </si>
   <si>
     <t>https://weeqp.azurewebsites.net/QP/WeeClaims/#/Emision</t>
   </si>
   <si>
-    <t>pruebasxj@yopmail.com</t>
-  </si>
-  <si>
-    <t>Emision 1</t>
-  </si>
-  <si>
-    <t>UrlClaims</t>
-  </si>
-  <si>
-    <t>CorreoClaims</t>
-  </si>
-  <si>
-    <t>ContrasenaClaims</t>
-  </si>
-  <si>
-    <t>FolioSolicitante</t>
-  </si>
-  <si>
     <t>923000003343</t>
   </si>
   <si>
-    <t>qahomxj1broker@yopmail.com</t>
-  </si>
-  <si>
-    <t>CapturaPreguntasPt2</t>
-  </si>
-  <si>
-    <t>Superior</t>
-  </si>
-  <si>
-    <t>Trimestral</t>
-  </si>
-  <si>
-    <t>Mensual</t>
+    <t>Cotizacion Superior Ultra Anual</t>
+  </si>
+  <si>
+    <t>Cotizacion Superior Ultra Semestral</t>
   </si>
   <si>
     <t>$2,000.00 / $4,000.00 US</t>
   </si>
   <si>
-    <t>$5,000.00 / $5,000.00 USD</t>
-  </si>
-  <si>
-    <t>$5,000.00 / $7,500.00 USD</t>
+    <t>Cotizacion Superior Ultra Trimestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Superior Ultra Mensual</t>
+  </si>
+  <si>
+    <t>Cotizacion Superior Open Anual</t>
   </si>
   <si>
     <t>Open</t>
   </si>
   <si>
-    <t>Cotizacion Superior Ultra Trimestral</t>
-  </si>
-  <si>
-    <t>Cotizacion Superior Ultra Mensual</t>
-  </si>
-  <si>
-    <t>Cotizacion Superior Open Anual</t>
-  </si>
-  <si>
     <t>Cotizacion Superior Open Semestral</t>
   </si>
   <si>
     <t>Cotizacion Superior Open Trimestral</t>
   </si>
   <si>
+    <t>Cotizacion Superior Open Mensual</t>
+  </si>
+  <si>
     <t>Cotizacion Optima Ultra Anual</t>
   </si>
   <si>
+    <t>Optima</t>
+  </si>
+  <si>
     <t>Cotizacion Optima Ultra Semestral</t>
   </si>
   <si>
@@ -343,101 +375,49 @@
     <t>Cotizacion Optima Ultra Mensual</t>
   </si>
   <si>
-    <t>Optima</t>
-  </si>
-  <si>
-    <t>Plus</t>
+    <t>Cotizacion Optima Plus Semestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Optima Plus Trimestral</t>
+  </si>
+  <si>
+    <t>Cotizacion Optima Plus Mensual</t>
   </si>
   <si>
     <t>Cotizacion Vital Plus Anual</t>
   </si>
   <si>
-    <t>Cotizacion  Vital Plus Semestral</t>
-  </si>
-  <si>
-    <t>Cotizacion  Vital Plus Trimestral</t>
-  </si>
-  <si>
-    <t>Cotizacion  Vital Plus Mensual</t>
-  </si>
-  <si>
-    <t>Cotizacion Vital Core Anual</t>
-  </si>
-  <si>
-    <t>Cotizacion Vital Core Semestral</t>
-  </si>
-  <si>
-    <t>Cotizacion Vital Core Trimestral</t>
-  </si>
-  <si>
-    <t>Cotizacion Vital Core Mensual</t>
-  </si>
-  <si>
-    <t>Core</t>
-  </si>
-  <si>
-    <t>Vital</t>
-  </si>
-  <si>
-    <t>Cotizacion Superior Ultra Semestral</t>
-  </si>
-  <si>
-    <t>Cotizacion Superior Ultra Anual</t>
-  </si>
-  <si>
-    <t>Cotizacion Superior Open Mensual</t>
-  </si>
-  <si>
-    <t>Eng</t>
-  </si>
-  <si>
-    <t>Cotizacion Optima Plus Anual</t>
-  </si>
-  <si>
-    <t>Cotizacion Optima Plus Semestral</t>
-  </si>
-  <si>
-    <t>Cotizacion Optima Plus Trimestral</t>
-  </si>
-  <si>
-    <t>Cotizacion Optima Plus Mensual</t>
-  </si>
-  <si>
-    <t>$2,000.00 / $4,000.00 USD</t>
+    <t>Cotizacion Individual Vital Plus Anual ESP</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>Cotizacion Individual Vital Plus Anual ENG</t>
+  </si>
+  <si>
+    <t>SI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -455,7 +435,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -476,21 +456,21 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
-    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="Hipervínculo" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -545,108 +525,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -658,23 +544,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -684,23 +570,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -708,26 +594,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -762,17 +645,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -787,33 +670,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -822,64 +680,64 @@
   <dimension ref="A1:DM13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" customWidth="1"/>
+    <col min="6" max="6" width="20.5" customWidth="1"/>
     <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5" customWidth="1"/>
+    <col min="9" max="9" width="11.1640625" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="15" max="15" width="17.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="26.5" customWidth="1"/>
+    <col min="18" max="18" width="23" customWidth="1"/>
+    <col min="19" max="19" width="24.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.6640625" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
+    <col min="22" max="22" width="17.1640625" customWidth="1"/>
+    <col min="23" max="23" width="8" customWidth="1"/>
+    <col min="24" max="24" width="17.1640625" customWidth="1"/>
+    <col min="25" max="25" width="24.33203125" customWidth="1"/>
+    <col min="26" max="26" width="17.1640625" customWidth="1"/>
     <col min="27" max="27" width="23.5" customWidth="1"/>
-    <col min="28" max="28" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="25" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="26" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.1640625" customWidth="1"/>
+    <col min="29" max="29" width="13.33203125" customWidth="1"/>
+    <col min="30" max="30" width="17.1640625" customWidth="1"/>
+    <col min="31" max="31" width="25" customWidth="1"/>
+    <col min="32" max="32" width="26" customWidth="1"/>
+    <col min="33" max="33" width="20.6640625" customWidth="1"/>
+    <col min="34" max="34" width="14.6640625" customWidth="1"/>
+    <col min="35" max="35" width="19.6640625" customWidth="1"/>
+    <col min="36" max="36" width="21.33203125" customWidth="1"/>
+    <col min="37" max="37" width="23.83203125" customWidth="1"/>
+    <col min="38" max="38" width="17.1640625" customWidth="1"/>
+    <col min="39" max="39" width="25.5" customWidth="1"/>
+    <col min="40" max="40" width="10.1640625" customWidth="1"/>
+    <col min="41" max="41" width="18.1640625" customWidth="1"/>
+    <col min="42" max="42" width="23.5" customWidth="1"/>
+    <col min="43" max="43" width="6.83203125" customWidth="1"/>
+    <col min="44" max="44" width="20.1640625" customWidth="1"/>
+    <col min="45" max="45" width="12.33203125" customWidth="1"/>
+    <col min="46" max="46" width="15.5" customWidth="1"/>
+    <col min="47" max="47" width="18.1640625" customWidth="1"/>
+    <col min="48" max="48" width="10.6640625" customWidth="1"/>
+    <col min="49" max="49" width="12.5" customWidth="1"/>
+    <col min="50" max="50" width="14.6640625" customWidth="1"/>
+    <col min="51" max="51" width="12.5" customWidth="1"/>
+    <col min="52" max="52" width="14.6640625" customWidth="1"/>
+    <col min="53" max="53" width="14" customWidth="1"/>
+    <col min="54" max="54" width="14.6640625" customWidth="1"/>
+    <col min="55" max="55" width="12.5" customWidth="1"/>
+    <col min="56" max="56" width="14.6640625" customWidth="1"/>
+    <col min="57" max="57" width="12.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
     <col min="59" max="59" width="27.33203125" customWidth="1"/>
     <col min="60" max="60" width="17.33203125" customWidth="1"/>
     <col min="61" max="61" width="21.1640625" customWidth="1"/>
@@ -938,304 +796,304 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
-      <c r="H1" t="s">
+      <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" t="s">
+      <c r="AR1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AS1" t="s">
         <v>36</v>
       </c>
-      <c r="J1" t="s">
+      <c r="AT1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AU1" t="s">
         <v>38</v>
       </c>
-      <c r="K1" t="s">
+      <c r="AV1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW1" t="s">
         <v>39</v>
       </c>
-      <c r="L1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N1" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" t="s">
-        <v>58</v>
-      </c>
-      <c r="P1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>60</v>
-      </c>
-      <c r="R1" t="s">
-        <v>61</v>
-      </c>
-      <c r="S1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T1" t="s">
-        <v>64</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="AX1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>43</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>44</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>46</v>
+      </c>
+      <c r="BE1" t="s">
         <v>47</v>
       </c>
-      <c r="V1" t="s">
-        <v>65</v>
-      </c>
-      <c r="W1" t="s">
+      <c r="BF1" t="s">
         <v>48</v>
-      </c>
-      <c r="X1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>20</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>18</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>21</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>17</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>22</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>16</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="J2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K2" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="L2" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="M2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X2" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD2" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG2" t="s">
         <v>72</v>
       </c>
       <c r="AH2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AK2" s="4"/>
       <c r="AM2" s="3"/>
       <c r="AO2" s="3"/>
       <c r="AP2" s="3"/>
       <c r="AR2" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS2" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX2">
         <v>100</v>
       </c>
       <c r="AY2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ2">
         <v>25</v>
       </c>
       <c r="BA2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB2">
         <v>20</v>
       </c>
       <c r="BC2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD2">
         <v>20</v>
       </c>
       <c r="BE2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF2">
         <v>10</v>
@@ -1243,155 +1101,155 @@
     </row>
     <row r="3" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="J3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="K3" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="L3" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="M3" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O3" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q3" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S3" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W3" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X3" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y3" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z3" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB3" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD3" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF3" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG3" t="s">
         <v>72</v>
       </c>
       <c r="AH3" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI3" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AK3" s="4"/>
       <c r="AM3" s="3"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
       <c r="AR3" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS3" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU3" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV3" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW3" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX3">
         <v>100</v>
       </c>
       <c r="AY3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ3">
         <v>25</v>
       </c>
       <c r="BA3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB3">
         <v>20</v>
       </c>
       <c r="BC3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD3">
         <v>20</v>
       </c>
       <c r="BE3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF3">
         <v>10</v>
@@ -1399,155 +1257,155 @@
     </row>
     <row r="4" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" t="s">
         <v>83</v>
       </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" t="s">
-        <v>112</v>
-      </c>
-      <c r="J4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K4" t="s">
-        <v>89</v>
-      </c>
-      <c r="L4" t="s">
-        <v>86</v>
-      </c>
       <c r="M4" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N4" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O4" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P4" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S4" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T4" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X4" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y4" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z4" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD4" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF4" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG4" t="s">
         <v>72</v>
       </c>
       <c r="AH4" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI4" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AK4" s="4"/>
       <c r="AM4" s="3"/>
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
       <c r="AR4" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS4" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT4" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU4" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV4" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW4" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX4">
         <v>100</v>
       </c>
       <c r="AY4" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ4">
         <v>25</v>
       </c>
       <c r="BA4" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB4">
         <v>20</v>
       </c>
       <c r="BC4" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD4">
         <v>20</v>
       </c>
       <c r="BE4" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF4">
         <v>10</v>
@@ -1555,262 +1413,262 @@
     </row>
     <row r="5" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G5" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I5" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="J5" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="K5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M5" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O5" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P5" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S5" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T5" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U5" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V5" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W5" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X5" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y5" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z5" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA5" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC5" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD5" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE5" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF5" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG5" t="s">
         <v>72</v>
       </c>
       <c r="AH5" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI5" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I6" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="J6" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="K6" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="L6" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="M6" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N6" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O6" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q6" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S6" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W6" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X6" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y6" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z6" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA6" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB6" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD6" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE6" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF6" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG6" t="s">
         <v>72</v>
       </c>
       <c r="AH6" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI6" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AK6" s="4"/>
       <c r="AM6" s="3"/>
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
       <c r="AR6" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS6" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU6" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV6" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW6" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX6">
         <v>100</v>
       </c>
       <c r="AY6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ6">
         <v>25</v>
       </c>
       <c r="BA6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB6">
         <v>20</v>
       </c>
       <c r="BC6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD6">
         <v>20</v>
       </c>
       <c r="BE6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF6">
         <v>10</v>
@@ -1818,155 +1676,155 @@
     </row>
     <row r="7" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I7" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="J7" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="K7" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="L7" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="M7" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q7" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U7" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V7" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X7" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z7" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA7" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB7" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC7" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD7" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE7" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG7" t="s">
         <v>72</v>
       </c>
       <c r="AH7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AK7" s="4"/>
       <c r="AM7" s="3"/>
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
       <c r="AR7" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS7" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU7" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV7" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX7">
         <v>100</v>
       </c>
       <c r="AY7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ7">
         <v>25</v>
       </c>
       <c r="BA7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB7">
         <v>20</v>
       </c>
       <c r="BC7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD7">
         <v>20</v>
       </c>
       <c r="BE7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF7">
         <v>10</v>
@@ -1974,155 +1832,155 @@
     </row>
     <row r="8" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" t="s">
         <v>83</v>
       </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" t="s">
-        <v>111</v>
-      </c>
-      <c r="K8" t="s">
-        <v>89</v>
-      </c>
-      <c r="L8" t="s">
-        <v>86</v>
-      </c>
       <c r="M8" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N8" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O8" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P8" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q8" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S8" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T8" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U8" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V8" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W8" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X8" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y8" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z8" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA8" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB8" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC8" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD8" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE8" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF8" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG8" t="s">
         <v>72</v>
       </c>
       <c r="AH8" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI8" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AK8" s="4"/>
       <c r="AM8" s="3"/>
       <c r="AO8" s="3"/>
       <c r="AP8" s="3"/>
       <c r="AR8" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS8" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT8" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU8" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV8" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW8" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX8">
         <v>100</v>
       </c>
       <c r="AY8" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ8">
         <v>25</v>
       </c>
       <c r="BA8" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB8">
         <v>20</v>
       </c>
       <c r="BC8" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD8">
         <v>20</v>
       </c>
       <c r="BE8" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF8">
         <v>10</v>
@@ -2130,118 +1988,253 @@
     </row>
     <row r="9" spans="1:117" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="J9" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="K9" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M9" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N9" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O9" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P9" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q9" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S9" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T9" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U9" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V9" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W9" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X9" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y9" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z9" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA9" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB9" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC9" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD9" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE9" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF9" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG9" t="s">
         <v>72</v>
       </c>
       <c r="AH9" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI9" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:117" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I10" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" t="s">
+        <v>62</v>
+      </c>
+      <c r="O10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P10" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R10" t="s">
+        <v>65</v>
+      </c>
+      <c r="S10" t="s">
+        <v>55</v>
+      </c>
+      <c r="T10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>63</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="DM10" s="2"/>
     </row>
     <row r="11" spans="1:117" x14ac:dyDescent="0.2">
-      <c r="G11" t="s">
-        <v>42</v>
+      <c r="A11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
+        <v>122</v>
+      </c>
+      <c r="I11" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11" t="s">
+        <v>62</v>
+      </c>
+      <c r="O11" t="s">
+        <v>55</v>
+      </c>
+      <c r="P11" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>64</v>
+      </c>
+      <c r="R11" t="s">
+        <v>65</v>
+      </c>
+      <c r="S11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>55</v>
       </c>
       <c r="AU11" s="2"/>
     </row>
@@ -2250,43 +2243,39 @@
     </row>
     <row r="13" spans="1:117" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BY2:BY9" xr:uid="{44F9EC80-62A4-4D27-A260-7E43580022DA}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BY2:BY9" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Intervención Psicosocial,Tratamiento Farmacológico,Ambos,No Aplica"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B6:B9" r:id="rId1" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{45957601-23AD-4501-AF0F-DD07D06BBC14}"/>
-    <hyperlink ref="B6" r:id="rId2" xr:uid="{46F897B8-AEA5-46E4-9E00-38627D387AAE}"/>
-    <hyperlink ref="D6" r:id="rId3" xr:uid="{06A466C3-D169-424D-8ED2-BB4617F2FFC9}"/>
-    <hyperlink ref="B7:B9" r:id="rId4" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{88DDC58F-C538-415D-B24B-CDFEA094129F}"/>
-    <hyperlink ref="D7" r:id="rId5" xr:uid="{68764909-E72A-4A4D-86DF-5924CA779A40}"/>
-    <hyperlink ref="D8" r:id="rId6" xr:uid="{E0FE90CB-C96E-4567-8471-28ACB3673D10}"/>
-    <hyperlink ref="D9" r:id="rId7" xr:uid="{7487188D-D7A9-4D3A-8893-B8B69F54129E}"/>
-    <hyperlink ref="B2" r:id="rId8" xr:uid="{0C92C0F9-A7AE-4D03-89F5-B286F2CC67BE}"/>
-    <hyperlink ref="D2" r:id="rId9" xr:uid="{C086842D-1602-4388-B16E-8B35D98150B3}"/>
-    <hyperlink ref="D3" r:id="rId10" xr:uid="{F6FA0EE4-4810-4469-AA62-8248A52A0517}"/>
-    <hyperlink ref="D4" r:id="rId11" xr:uid="{1480D6B5-121E-46AB-98A2-9195F59438CE}"/>
-    <hyperlink ref="D5" r:id="rId12" xr:uid="{5A24B62D-E43E-4FE0-8B18-0A7DE3231746}"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D7" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="D8" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="D9" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91658F97-1B63-4028-A047-57A0079160D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="23.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="54.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="23.33203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="4" customWidth="1"/>
+    <col min="4" max="4" width="54.1640625" style="4" customWidth="1"/>
     <col min="5" max="5" width="17.1640625" style="4" customWidth="1"/>
     <col min="6" max="16384" width="11.5" style="4"/>
   </cols>
@@ -2296,34 +2285,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="AE1" s="5"/>
     </row>
     <row r="2" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="AE2" s="5"/>
     </row>
@@ -2335,15 +2324,15 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" location="/Emision" xr:uid="{D71A8889-939C-462C-B9FE-A8259BE91E93}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{47DEFC80-EEF9-4ED6-8004-D8C9C8297C1F}"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89217B83-F5AC-41B7-85ED-07DFA2DFDFF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BF24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2352,155 +2341,155 @@
   <sheetData>
     <row r="1" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E1" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="J1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K1" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="L1" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="M1" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O1" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q1" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S1" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V1" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z1" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF1" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG1" t="s">
         <v>72</v>
       </c>
       <c r="AH1" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK1" s="4"/>
       <c r="AM1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
       <c r="AR1" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS1" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU1" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV1" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW1" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX1">
         <v>100</v>
       </c>
       <c r="AY1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ1">
         <v>25</v>
       </c>
       <c r="BA1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB1">
         <v>20</v>
       </c>
       <c r="BC1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD1">
         <v>20</v>
       </c>
       <c r="BE1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF1">
         <v>10</v>
@@ -2508,155 +2497,155 @@
     </row>
     <row r="2" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="J2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="L2" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X2" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD2" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG2" t="s">
         <v>72</v>
       </c>
       <c r="AH2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK2" s="4"/>
       <c r="AM2" s="3"/>
       <c r="AO2" s="3"/>
       <c r="AP2" s="3"/>
       <c r="AR2" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS2" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX2">
         <v>100</v>
       </c>
       <c r="AY2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ2">
         <v>25</v>
       </c>
       <c r="BA2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB2">
         <v>20</v>
       </c>
       <c r="BC2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD2">
         <v>20</v>
       </c>
       <c r="BE2" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF2">
         <v>10</v>
@@ -2664,155 +2653,155 @@
     </row>
     <row r="3" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" t="s">
         <v>83</v>
       </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" t="s">
-        <v>89</v>
-      </c>
-      <c r="L3" t="s">
-        <v>86</v>
-      </c>
       <c r="M3" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O3" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q3" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S3" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W3" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X3" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y3" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z3" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB3" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD3" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF3" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG3" t="s">
         <v>72</v>
       </c>
       <c r="AH3" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK3" s="4"/>
       <c r="AM3" s="3"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
       <c r="AR3" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS3" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU3" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV3" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW3" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX3">
         <v>100</v>
       </c>
       <c r="AY3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ3">
         <v>25</v>
       </c>
       <c r="BA3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB3">
         <v>20</v>
       </c>
       <c r="BC3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD3">
         <v>20</v>
       </c>
       <c r="BE3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF3">
         <v>10</v>
@@ -2820,262 +2809,262 @@
     </row>
     <row r="4" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G4" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" t="s">
         <v>85</v>
       </c>
-      <c r="J4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" t="s">
-        <v>90</v>
-      </c>
       <c r="L4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M4" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N4" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O4" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P4" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S4" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T4" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X4" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y4" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z4" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD4" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF4" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG4" t="s">
         <v>72</v>
       </c>
       <c r="AH4" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI4" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G5" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I5" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="J5" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="L5" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="M5" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O5" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P5" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S5" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T5" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U5" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V5" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W5" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X5" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y5" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z5" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA5" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC5" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD5" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE5" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF5" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG5" t="s">
         <v>72</v>
       </c>
       <c r="AH5" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI5" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK5" s="4"/>
       <c r="AM5" s="3"/>
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
       <c r="AR5" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS5" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT5" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU5" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV5" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW5" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX5">
         <v>100</v>
       </c>
       <c r="AY5" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ5">
         <v>25</v>
       </c>
       <c r="BA5" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB5">
         <v>20</v>
       </c>
       <c r="BC5" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD5">
         <v>20</v>
       </c>
       <c r="BE5" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF5">
         <v>10</v>
@@ -3083,155 +3072,155 @@
     </row>
     <row r="6" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I6" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="J6" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="K6" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="M6" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N6" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O6" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q6" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S6" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W6" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X6" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y6" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z6" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA6" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB6" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD6" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE6" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF6" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG6" t="s">
         <v>72</v>
       </c>
       <c r="AH6" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK6" s="4"/>
       <c r="AM6" s="3"/>
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
       <c r="AR6" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS6" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU6" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV6" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW6" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX6">
         <v>100</v>
       </c>
       <c r="AY6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ6">
         <v>25</v>
       </c>
       <c r="BA6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB6">
         <v>20</v>
       </c>
       <c r="BC6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD6">
         <v>20</v>
       </c>
       <c r="BE6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF6">
         <v>10</v>
@@ -3239,155 +3228,155 @@
     </row>
     <row r="7" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" t="s">
         <v>83</v>
       </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J7" t="s">
-        <v>91</v>
-      </c>
-      <c r="K7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L7" t="s">
-        <v>86</v>
-      </c>
       <c r="M7" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q7" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U7" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V7" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X7" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z7" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA7" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB7" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC7" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD7" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE7" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG7" t="s">
         <v>72</v>
       </c>
       <c r="AH7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK7" s="4"/>
       <c r="AM7" s="3"/>
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
       <c r="AR7" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS7" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU7" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV7" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX7">
         <v>100</v>
       </c>
       <c r="AY7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ7">
         <v>25</v>
       </c>
       <c r="BA7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB7">
         <v>20</v>
       </c>
       <c r="BC7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD7">
         <v>20</v>
       </c>
       <c r="BE7" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF7">
         <v>10</v>
@@ -3395,262 +3384,262 @@
     </row>
     <row r="8" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G8" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" t="s">
+        <v>108</v>
+      </c>
+      <c r="K8" t="s">
         <v>85</v>
       </c>
-      <c r="J8" t="s">
-        <v>91</v>
-      </c>
-      <c r="K8" t="s">
-        <v>90</v>
-      </c>
       <c r="L8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M8" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N8" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O8" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P8" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q8" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S8" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T8" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U8" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V8" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W8" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X8" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y8" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z8" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA8" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB8" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC8" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD8" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE8" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF8" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG8" t="s">
         <v>72</v>
       </c>
       <c r="AH8" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI8" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="J9" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="L9" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="M9" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N9" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O9" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P9" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q9" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S9" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T9" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U9" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V9" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W9" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X9" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y9" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z9" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA9" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB9" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC9" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD9" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE9" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF9" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG9" t="s">
         <v>72</v>
       </c>
       <c r="AH9" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI9" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK9" s="4"/>
       <c r="AM9" s="3"/>
       <c r="AO9" s="3"/>
       <c r="AP9" s="3"/>
       <c r="AR9" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS9" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT9" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU9" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV9" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW9" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX9">
         <v>100</v>
       </c>
       <c r="AY9" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ9">
         <v>25</v>
       </c>
       <c r="BA9" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB9">
         <v>20</v>
       </c>
       <c r="BC9" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD9">
         <v>20</v>
       </c>
       <c r="BE9" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF9">
         <v>10</v>
@@ -3658,155 +3647,155 @@
     </row>
     <row r="10" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I10" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="J10" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K10" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="L10" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="M10" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N10" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O10" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P10" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q10" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S10" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T10" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U10" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V10" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W10" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X10" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y10" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z10" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA10" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB10" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC10" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD10" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE10" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF10" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG10" t="s">
         <v>72</v>
       </c>
       <c r="AH10" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI10" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK10" s="4"/>
       <c r="AM10" s="3"/>
       <c r="AO10" s="3"/>
       <c r="AP10" s="3"/>
       <c r="AR10" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS10" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT10" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU10" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV10" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW10" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX10">
         <v>100</v>
       </c>
       <c r="AY10" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ10">
         <v>25</v>
       </c>
       <c r="BA10" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB10">
         <v>20</v>
       </c>
       <c r="BC10" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD10">
         <v>20</v>
       </c>
       <c r="BE10" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF10">
         <v>10</v>
@@ -3814,155 +3803,155 @@
     </row>
     <row r="11" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J11" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" t="s">
         <v>83</v>
       </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" t="s">
-        <v>89</v>
-      </c>
-      <c r="L11" t="s">
-        <v>86</v>
-      </c>
       <c r="M11" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N11" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O11" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P11" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S11" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T11" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U11" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V11" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W11" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X11" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y11" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z11" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB11" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC11" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD11" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE11" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF11" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG11" t="s">
         <v>72</v>
       </c>
       <c r="AH11" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI11" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK11" s="4"/>
       <c r="AM11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
       <c r="AR11" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS11" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT11" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU11" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV11" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW11" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX11">
         <v>100</v>
       </c>
       <c r="AY11" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ11">
         <v>25</v>
       </c>
       <c r="BA11" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB11">
         <v>20</v>
       </c>
       <c r="BC11" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD11">
         <v>20</v>
       </c>
       <c r="BE11" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF11">
         <v>10</v>
@@ -3970,262 +3959,262 @@
     </row>
     <row r="12" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G12" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H12" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I12" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K12" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N12" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O12" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P12" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q12" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S12" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T12" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U12" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V12" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W12" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X12" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y12" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z12" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA12" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC12" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD12" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE12" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF12" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG12" t="s">
         <v>72</v>
       </c>
       <c r="AH12" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI12" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G13" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I13" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="J13" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="K13" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="L13" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="M13" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N13" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O13" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P13" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q13" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S13" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T13" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U13" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V13" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W13" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X13" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y13" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z13" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA13" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB13" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC13" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD13" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE13" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF13" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG13" t="s">
         <v>72</v>
       </c>
       <c r="AH13" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI13" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK13" s="4"/>
       <c r="AM13" s="3"/>
       <c r="AO13" s="3"/>
       <c r="AP13" s="3"/>
       <c r="AR13" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS13" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT13" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU13" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV13" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW13" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX13">
         <v>100</v>
       </c>
       <c r="AY13" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ13">
         <v>25</v>
       </c>
       <c r="BA13" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB13">
         <v>20</v>
       </c>
       <c r="BC13" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD13">
         <v>20</v>
       </c>
       <c r="BE13" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF13">
         <v>10</v>
@@ -4233,155 +4222,155 @@
     </row>
     <row r="14" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G14" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H14" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I14" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="J14" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="K14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="L14" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="M14" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N14" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O14" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P14" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q14" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S14" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T14" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U14" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V14" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W14" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X14" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y14" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z14" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA14" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB14" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC14" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD14" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE14" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF14" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG14" t="s">
         <v>72</v>
       </c>
       <c r="AH14" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI14" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK14" s="4"/>
       <c r="AM14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
       <c r="AR14" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS14" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT14" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU14" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV14" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW14" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX14">
         <v>100</v>
       </c>
       <c r="AY14" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ14">
         <v>25</v>
       </c>
       <c r="BA14" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB14">
         <v>20</v>
       </c>
       <c r="BC14" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD14">
         <v>20</v>
       </c>
       <c r="BE14" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF14">
         <v>10</v>
@@ -4389,155 +4378,155 @@
     </row>
     <row r="15" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" t="s">
+        <v>113</v>
+      </c>
+      <c r="J15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" t="s">
         <v>83</v>
       </c>
-      <c r="E15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" t="s">
-        <v>101</v>
-      </c>
-      <c r="J15" t="s">
-        <v>102</v>
-      </c>
-      <c r="K15" t="s">
-        <v>89</v>
-      </c>
-      <c r="L15" t="s">
-        <v>86</v>
-      </c>
       <c r="M15" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N15" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O15" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P15" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q15" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S15" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T15" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U15" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V15" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W15" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X15" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y15" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z15" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA15" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB15" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC15" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD15" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE15" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF15" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG15" t="s">
         <v>72</v>
       </c>
       <c r="AH15" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI15" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK15" s="4"/>
       <c r="AM15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
       <c r="AR15" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS15" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT15" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU15" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV15" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW15" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX15">
         <v>100</v>
       </c>
       <c r="AY15" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ15">
         <v>25</v>
       </c>
       <c r="BA15" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB15">
         <v>20</v>
       </c>
       <c r="BC15" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD15">
         <v>20</v>
       </c>
       <c r="BE15" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF15">
         <v>10</v>
@@ -4545,262 +4534,262 @@
     </row>
     <row r="16" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G16" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H16" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I16" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="J16" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N16" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O16" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P16" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q16" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S16" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T16" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U16" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V16" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W16" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X16" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y16" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z16" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA16" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB16" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC16" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD16" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE16" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF16" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG16" t="s">
         <v>72</v>
       </c>
       <c r="AH16" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI16" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G17" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H17" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I17" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="J17" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="K17" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="L17" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="M17" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N17" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O17" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P17" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q17" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S17" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T17" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U17" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V17" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W17" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X17" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y17" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z17" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA17" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB17" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC17" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD17" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE17" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF17" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG17" t="s">
         <v>72</v>
       </c>
       <c r="AH17" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI17" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK17" s="4"/>
       <c r="AM17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
       <c r="AR17" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS17" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT17" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU17" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV17" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW17" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX17">
         <v>100</v>
       </c>
       <c r="AY17" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ17">
         <v>25</v>
       </c>
       <c r="BA17" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB17">
         <v>20</v>
       </c>
       <c r="BC17" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD17">
         <v>20</v>
       </c>
       <c r="BE17" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF17">
         <v>10</v>
@@ -4808,155 +4797,155 @@
     </row>
     <row r="18" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" t="s">
+        <v>78</v>
+      </c>
+      <c r="J18" t="s">
+        <v>79</v>
+      </c>
+      <c r="K18" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" t="s">
-        <v>5</v>
-      </c>
-      <c r="H18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" t="s">
-        <v>112</v>
-      </c>
-      <c r="J18" t="s">
-        <v>102</v>
-      </c>
-      <c r="K18" t="s">
-        <v>88</v>
-      </c>
       <c r="L18" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="M18" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N18" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O18" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P18" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q18" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S18" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T18" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U18" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V18" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W18" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X18" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y18" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z18" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA18" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB18" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC18" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD18" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE18" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF18" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG18" t="s">
         <v>72</v>
       </c>
       <c r="AH18" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI18" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK18" s="4"/>
       <c r="AM18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
       <c r="AR18" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS18" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT18" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU18" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV18" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW18" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX18">
         <v>100</v>
       </c>
       <c r="AY18" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ18">
         <v>25</v>
       </c>
       <c r="BA18" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB18">
         <v>20</v>
       </c>
       <c r="BC18" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD18">
         <v>20</v>
       </c>
       <c r="BE18" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF18">
         <v>10</v>
@@ -4964,155 +4953,155 @@
     </row>
     <row r="19" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" t="s">
+        <v>78</v>
+      </c>
+      <c r="J19" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" t="s">
+        <v>59</v>
+      </c>
+      <c r="L19" t="s">
         <v>83</v>
       </c>
-      <c r="E19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" t="s">
-        <v>5</v>
-      </c>
-      <c r="H19" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" t="s">
-        <v>112</v>
-      </c>
-      <c r="J19" t="s">
-        <v>102</v>
-      </c>
-      <c r="K19" t="s">
-        <v>89</v>
-      </c>
-      <c r="L19" t="s">
-        <v>86</v>
-      </c>
       <c r="M19" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N19" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O19" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P19" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q19" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S19" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T19" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U19" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V19" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W19" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X19" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y19" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z19" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA19" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB19" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC19" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD19" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE19" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF19" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG19" t="s">
         <v>72</v>
       </c>
       <c r="AH19" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI19" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK19" s="4"/>
       <c r="AM19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
       <c r="AR19" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS19" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT19" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU19" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV19" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW19" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX19">
         <v>100</v>
       </c>
       <c r="AY19" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ19">
         <v>25</v>
       </c>
       <c r="BA19" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB19">
         <v>20</v>
       </c>
       <c r="BC19" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD19">
         <v>20</v>
       </c>
       <c r="BE19" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF19">
         <v>10</v>
@@ -5120,262 +5109,262 @@
     </row>
     <row r="20" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G20" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H20" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I20" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="J20" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="K20" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N20" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O20" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P20" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q20" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R20" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S20" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T20" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U20" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V20" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W20" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X20" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y20" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z20" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA20" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB20" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC20" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD20" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE20" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF20" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG20" t="s">
         <v>72</v>
       </c>
       <c r="AH20" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI20" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G21" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H21" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I21" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="J21" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="L21" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="M21" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N21" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O21" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P21" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q21" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S21" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T21" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U21" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V21" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W21" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X21" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y21" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z21" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA21" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB21" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC21" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD21" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE21" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF21" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG21" t="s">
         <v>72</v>
       </c>
       <c r="AH21" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI21" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK21" s="4"/>
       <c r="AM21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
       <c r="AR21" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS21" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT21" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU21" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV21" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW21" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX21">
         <v>100</v>
       </c>
       <c r="AY21" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ21">
         <v>25</v>
       </c>
       <c r="BA21" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB21">
         <v>20</v>
       </c>
       <c r="BC21" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD21">
         <v>20</v>
       </c>
       <c r="BE21" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF21">
         <v>10</v>
@@ -5383,155 +5372,155 @@
     </row>
     <row r="22" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G22" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H22" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I22" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="J22" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="M22" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N22" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O22" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P22" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q22" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R22" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S22" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T22" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U22" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V22" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W22" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X22" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y22" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z22" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA22" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB22" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC22" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD22" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE22" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF22" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG22" t="s">
         <v>72</v>
       </c>
       <c r="AH22" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI22" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK22" s="4"/>
       <c r="AM22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
       <c r="AR22" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS22" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT22" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU22" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV22" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW22" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX22">
         <v>100</v>
       </c>
       <c r="AY22" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ22">
         <v>25</v>
       </c>
       <c r="BA22" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB22">
         <v>20</v>
       </c>
       <c r="BC22" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD22">
         <v>20</v>
       </c>
       <c r="BE22" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF22">
         <v>10</v>
@@ -5539,155 +5528,155 @@
     </row>
     <row r="23" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J23" t="s">
+        <v>88</v>
+      </c>
+      <c r="K23" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" t="s">
         <v>83</v>
       </c>
-      <c r="E23" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H23" t="s">
-        <v>35</v>
-      </c>
-      <c r="I23" t="s">
-        <v>112</v>
-      </c>
-      <c r="J23" t="s">
-        <v>111</v>
-      </c>
-      <c r="K23" t="s">
-        <v>89</v>
-      </c>
-      <c r="L23" t="s">
-        <v>86</v>
-      </c>
       <c r="M23" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N23" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O23" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P23" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q23" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S23" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T23" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U23" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V23" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W23" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X23" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y23" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z23" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA23" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB23" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC23" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD23" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE23" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF23" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG23" t="s">
         <v>72</v>
       </c>
       <c r="AH23" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI23" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AK23" s="4"/>
       <c r="AM23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
       <c r="AR23" s="3" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="AS23" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AT23" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AU23" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="AV23" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="AW23" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AX23">
         <v>100</v>
       </c>
       <c r="AY23" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AZ23">
         <v>25</v>
       </c>
       <c r="BA23" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BB23">
         <v>20</v>
       </c>
       <c r="BC23" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BD23">
         <v>20</v>
       </c>
       <c r="BE23" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BF23">
         <v>10</v>
@@ -5695,154 +5684,148 @@
     </row>
     <row r="24" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G24" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H24" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I24" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="J24" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="N24" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O24" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P24" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Q24" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R24" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="S24" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="T24" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="U24" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="V24" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="W24" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="X24" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Y24" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Z24" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA24" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB24" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AC24" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AD24" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AE24" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AF24" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AG24" t="s">
         <v>72</v>
       </c>
       <c r="AH24" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="AI24" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BY1:BY24" xr:uid="{DC9C344B-BDE6-4A60-B8FB-2D4AAF4F3344}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BY1:BY24" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Intervención Psicosocial,Tratamiento Farmacológico,Ambos,No Aplica"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B5:B8" r:id="rId1" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{20A6198B-F417-40A8-8627-8668F560453D}"/>
-    <hyperlink ref="B5" r:id="rId2" xr:uid="{33736C83-7E2A-4A90-9642-EA8B66327004}"/>
-    <hyperlink ref="D5" r:id="rId3" xr:uid="{694169EE-5731-4358-94B1-4A45CE7CF1F2}"/>
-    <hyperlink ref="B6:B8" r:id="rId4" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{08551A9D-3F12-468F-A6B4-E4CC71F9AAE3}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{DDF8E31A-CBA3-4CA4-84E0-BAB944823E35}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{BFE70029-719A-4A66-AA8C-601CDAF85BB2}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{6DC83D43-81D3-4679-A819-D107E8AFFD5A}"/>
-    <hyperlink ref="B1" r:id="rId8" xr:uid="{8D346009-13BF-40A9-A873-46AE105E0BB3}"/>
-    <hyperlink ref="D1" r:id="rId9" xr:uid="{A86FB013-E363-4C0E-B7E8-2F180AC376D3}"/>
-    <hyperlink ref="D2" r:id="rId10" xr:uid="{6AC40481-6564-457B-AFF8-03D60A0E2A3E}"/>
-    <hyperlink ref="D3" r:id="rId11" xr:uid="{4A97FE31-C8B6-4D6C-80CB-2C3FFF3779BE}"/>
-    <hyperlink ref="D4" r:id="rId12" xr:uid="{7A504388-E6B6-4965-8C3E-5069DC4AE63E}"/>
-    <hyperlink ref="B13:B16" r:id="rId13" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{FB366572-567F-46A4-B130-0A9F448F53EB}"/>
-    <hyperlink ref="B13" r:id="rId14" xr:uid="{B7D75009-FE2A-4F52-825E-D16674ED2C18}"/>
-    <hyperlink ref="D13" r:id="rId15" xr:uid="{9F5D899A-90CA-462F-A123-DE8FF6ADA3AF}"/>
-    <hyperlink ref="B14:B16" r:id="rId16" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{503CD5EA-A59B-4657-AF78-E8EDFCEB3C7D}"/>
-    <hyperlink ref="D14" r:id="rId17" xr:uid="{C10065F1-A661-4718-AC02-1E3C04DEB43B}"/>
-    <hyperlink ref="D15" r:id="rId18" xr:uid="{A27C6F4D-6087-448A-A2B6-A656F9B401D0}"/>
-    <hyperlink ref="D16" r:id="rId19" xr:uid="{5490F5B0-B9FA-4EDF-BE9A-8534DEE273F1}"/>
-    <hyperlink ref="B9" r:id="rId20" xr:uid="{8BF6DE7B-784D-436B-84CD-8E0BDFC5D95F}"/>
-    <hyperlink ref="D9" r:id="rId21" xr:uid="{1C2AB6D8-0E19-4FFB-824C-3DCA679C066D}"/>
-    <hyperlink ref="D10" r:id="rId22" xr:uid="{F10AC502-37F1-4BB0-A68E-C196D526AECC}"/>
-    <hyperlink ref="D11" r:id="rId23" xr:uid="{FF0CCA05-15B2-4F7E-BE07-58AD34A386F9}"/>
-    <hyperlink ref="D12" r:id="rId24" xr:uid="{1B62D41E-E8C4-43CC-B4A6-131682ECCC91}"/>
-    <hyperlink ref="B21:B24" r:id="rId25" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{AB2BF27A-9A89-4139-849D-536F0F2D0F65}"/>
-    <hyperlink ref="B21" r:id="rId26" xr:uid="{195118D5-492D-45AB-A9BB-00B625F83014}"/>
-    <hyperlink ref="D21" r:id="rId27" xr:uid="{D05EC650-1ADB-40A9-8BAB-AB68CD9207FF}"/>
-    <hyperlink ref="B22:B24" r:id="rId28" display="https://weeqp.azurewebsites.net/AF/Broker/Login/Auth" xr:uid="{DF6EBDA2-5C33-417A-A0CF-87058027C43A}"/>
-    <hyperlink ref="D22" r:id="rId29" xr:uid="{BD092C6F-EA87-473B-A25D-A9FEE2659DBC}"/>
-    <hyperlink ref="D23" r:id="rId30" xr:uid="{5BC6C16E-C9C8-43F3-949E-1A5655A8F29C}"/>
-    <hyperlink ref="D24" r:id="rId31" xr:uid="{7D2902C0-9E4E-4362-A806-3694D9F105A6}"/>
-    <hyperlink ref="B17" r:id="rId32" xr:uid="{C50F52EB-0927-4BD7-A8A7-8404907C67F5}"/>
-    <hyperlink ref="D17" r:id="rId33" xr:uid="{23AEE11B-7EC0-45F5-9FCA-CEE9A29F1D3D}"/>
-    <hyperlink ref="D18" r:id="rId34" xr:uid="{D3A2FD01-F010-4D3A-AAE0-B3CEB9EEF1C3}"/>
-    <hyperlink ref="D19" r:id="rId35" xr:uid="{2EB6034D-1D7F-416A-A1BD-FBA3DA2D4A23}"/>
-    <hyperlink ref="D20" r:id="rId36" xr:uid="{A25451EE-8204-44B5-99A4-957D06A93504}"/>
+    <hyperlink ref="B1" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="D1" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="D2" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="D3" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="D4" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="B5" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="D5" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="D6" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="D7" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="D8" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
+    <hyperlink ref="B9" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
+    <hyperlink ref="D9" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
+    <hyperlink ref="D10" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
+    <hyperlink ref="D11" r:id="rId14" xr:uid="{00000000-0004-0000-0200-00000D000000}"/>
+    <hyperlink ref="D12" r:id="rId15" xr:uid="{00000000-0004-0000-0200-00000E000000}"/>
+    <hyperlink ref="B13" r:id="rId16" xr:uid="{00000000-0004-0000-0200-00000F000000}"/>
+    <hyperlink ref="D13" r:id="rId17" xr:uid="{00000000-0004-0000-0200-000010000000}"/>
+    <hyperlink ref="D14" r:id="rId18" xr:uid="{00000000-0004-0000-0200-000011000000}"/>
+    <hyperlink ref="D15" r:id="rId19" xr:uid="{00000000-0004-0000-0200-000012000000}"/>
+    <hyperlink ref="D16" r:id="rId20" xr:uid="{00000000-0004-0000-0200-000013000000}"/>
+    <hyperlink ref="B17" r:id="rId21" xr:uid="{00000000-0004-0000-0200-000014000000}"/>
+    <hyperlink ref="D17" r:id="rId22" xr:uid="{00000000-0004-0000-0200-000015000000}"/>
+    <hyperlink ref="D18" r:id="rId23" xr:uid="{00000000-0004-0000-0200-000016000000}"/>
+    <hyperlink ref="D19" r:id="rId24" xr:uid="{00000000-0004-0000-0200-000017000000}"/>
+    <hyperlink ref="D20" r:id="rId25" xr:uid="{00000000-0004-0000-0200-000018000000}"/>
+    <hyperlink ref="B21" r:id="rId26" xr:uid="{00000000-0004-0000-0200-000019000000}"/>
+    <hyperlink ref="D21" r:id="rId27" xr:uid="{00000000-0004-0000-0200-00001A000000}"/>
+    <hyperlink ref="D22" r:id="rId28" xr:uid="{00000000-0004-0000-0200-00001B000000}"/>
+    <hyperlink ref="D23" r:id="rId29" xr:uid="{00000000-0004-0000-0200-00001C000000}"/>
+    <hyperlink ref="D24" r:id="rId30" xr:uid="{00000000-0004-0000-0200-00001D000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
